--- a/tools/记账本文案.xlsx
+++ b/tools/记账本文案.xlsx
@@ -13,7 +13,7 @@
     <sheet name="未列入" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'界面文字'!$A$3:$F$529</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'界面文字'!$A$3:$F$517</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'导出文件里的文字'!$A$3:$F$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'未列入'!$A$3:$D$210</definedName>
   </definedNames>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F529"/>
+  <dimension ref="A1:F517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>创建账本</t>
+          <t>仅计算累计收入与支出，适合统计长期费用，无余额功能。</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>只累计收入和支出，不涉及账户，首页显示本月收支。</t>
+          <t>创建账本</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>有账户和余额，可以设每月生活费，首页显示「预算剩余」。</t>
+          <t>增加账户与预算功能，适合日常生活费统计等。</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -692,7 +692,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>每个账本独立统计。之后可以再建账本，在「设置 → 账本」里切换。</t>
+          <t>每个账本独立统计。可在「设置 → 账本」里新建账本。</t>
         </is>
       </c>
       <c r="F9" s="5" t="n"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>点这里填写每月生活费，首页就会显示「预算剩余」和日均可用。</t>
+          <t>点击填写每月预算。</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>点这里设置每月生活费，就能看到「预算剩余」和日均可用</t>
+          <t>点击设置每月预算。</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>还没有设置生活费</t>
+          <t>还没有设置预算</t>
         </is>
       </c>
       <c r="F21" s="5" t="n"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>{monthLabel} 生活费</t>
+          <t>{monthLabel} 预算</t>
         </is>
       </c>
       <c r="F23" s="5" t="n"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>填每月到手的钱。之后没设置的月份会自动沿用这一次的额度。</t>
+          <t>输入每月预算，后续月份若未单独设置将沿用此数值</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>点右下角的按钮开始记一笔</t>
+          <t>本月没有记录</t>
         </is>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>这个月还没有记录</t>
+          <t>点[+]开始记一笔</t>
         </is>
       </c>
       <c r="F31" s="5" t="n"/>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>改回当前时间</t>
+          <t>记账时间</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Date Time Dialog</t>
+          <t>Monthly Panel</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>记账时间</t>
+          <t>每期约 {Money.formatWithSymbol(state.planPerPeriodCents)}，到期自动生成扣款</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Monthly Panel</t>
+          <t>Monthly Panel；导出与备份 · Target Field；月付 / 分期 · Category Picker Field 等4处</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>每期约 {Money.formatWithSymbol(state.planPerPeriodCents)}，到期自动生成扣款</t>
+          <t>▾</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Monthly Panel；导出与备份 · Target Field；月付 / 分期 · Category Picker Field 等4处</t>
+          <t>Monthly Panel；月付 / 分期 · Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>▾</t>
+          <t>关联类别</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>关联类别</t>
+          <t>期数</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Monthly Panel；月付 / 分期 · Installment Editor Dialog</t>
+          <t>Save Button</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>期数</t>
+          <t>创建月付</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>创建月付</t>
+          <t>填写名称、期数和还款日</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>填写名称、期数和还款日</t>
+          <t>选择分类和账户</t>
         </is>
       </c>
       <c r="F59" s="5" t="n"/>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>选择分类和账户</t>
+          <t>选择转出和转入账户</t>
         </is>
       </c>
       <c r="F60" s="5" t="n"/>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Save Button</t>
+          <t>Transfer Panel</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>选择转出和转入账户</t>
+          <t>转账不计入收支，仅手续费算入支出。</t>
         </is>
       </c>
       <c r="F61" s="5" t="n"/>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>转账不计入收支，只有手续费算支出。</t>
+          <t>需要至少两个账户才能转账</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -2086,69 +2086,69 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Transfer Panel</t>
+          <t>记账页；导出与备份 · Source Label；导入账单 · Source Label 等4处</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>需要至少两个账户才能转账</t>
+          <t>月付</t>
         </is>
       </c>
       <c r="F63" s="5" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n">
+      <c r="A64" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>记账页</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>记账页；导出与备份 · Source Label；导入账单 · Source Label 等4处</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>选项名称</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>月付</t>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>编辑账单</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Category Chips</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>没有可选分类</t>
         </is>
       </c>
       <c r="F64" s="5" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>编辑账单</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Category Chips</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>没有可选分类</t>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Date Time Fields</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>%02d:%02d（原始时间）</t>
         </is>
       </c>
       <c r="F65" s="5" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>%02d:%02d（原始时间）</t>
+          <t>改回当前时间</t>
         </is>
       </c>
       <c r="F66" s="5" t="n"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Date Time Fields</t>
+          <t>Date Time Fields；记账页 · Date Time Dialog；搜索 · Search Screen</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>改回原始时间</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="F67" s="5" t="n"/>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Date Time Fields；记账页 · Date Time Dialog；搜索 · Search Screen</t>
+          <t>Edit Header</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>编辑记录</t>
         </is>
       </c>
       <c r="F68" s="5" t="n"/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Edit Header</t>
+          <t>Edit Header；记账页 · Entry Header；记账页 · Category More Dialog 等4处</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>编辑记录</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="F69" s="5" t="n"/>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Edit Header；记账页 · Entry Header；记账页 · Category More Dialog 等4处</t>
+          <t>Edit Screen</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>删除这笔记录</t>
         </is>
       </c>
       <c r="F70" s="5" t="n"/>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen</t>
+          <t>Edit Screen；记账页 · Transfer Panel</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>删除这笔记录</t>
+          <t>从</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -2320,17 +2320,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen</t>
+          <t>Edit Screen；记账页 · Transfer Panel</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>比如退款、账户互转，记下来但不进统计。</t>
+          <t>到</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen</t>
+          <t>Edit Screen；记账页 · Transfer Panel；月付 / 分期 · Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>这笔记录删除后，余额和统计会立刻跟着更新。</t>
+          <t>手续费（可留空）</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -2372,17 +2372,17 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen；记账页 · Transfer Panel</t>
+          <t>Edit Screen；首页 / 记账 · Allowance Dialog；搜索 · Search Screen</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>从</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -2398,17 +2398,17 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen；记账页 · Transfer Panel</t>
+          <t>Save Row</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>到</t>
+          <t>保存 {Money.formatWithSymbol(amountCents)}</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen；记账页 · Transfer Panel；月付 / 分期 · Installment Editor Dialog</t>
+          <t>Save Row</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>手续费（可留空）</t>
+          <t>请填写金额、分类和账户</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Edit Screen；首页 / 记账 · Allowance Dialog；搜索 · Search Screen</t>
+          <t>Type Row；记账页 · Save Button；记账页 等6处</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -2460,33 +2460,33 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>转账</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n">
+      <c r="A78" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>编辑账单</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Save Row</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>保存 {Money.formatWithSymbol(amountCents)}</t>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>账单详情</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Amount Card；编辑账单 · Edit Screen；首页 / 记账 · Transaction Row Item</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>不计收支</t>
         </is>
       </c>
       <c r="F78" s="5" t="n"/>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>编辑账单</t>
+          <t>账单详情</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Save Row</t>
+          <t>DATE_FORMAT</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>金额、分类和账户都要填</t>
+          <t>yyyy年M月d日 EEE</t>
         </is>
       </c>
       <c r="F79" s="5" t="n"/>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>编辑账单</t>
+          <t>账单详情</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Type Row；记账页 · Save Button；记账页 等6处</t>
+          <t>Detail Screen</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -2538,33 +2538,33 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>转账</t>
+          <t>修改</t>
         </is>
       </c>
       <c r="F80" s="5" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>账单详情</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Amount Card；编辑账单 · Edit Screen；首页 / 记账 · Transaction Row Item</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>不计收支</t>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Detail Screen</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>记录详情</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>DATE_FORMAT</t>
+          <t>Detail Screen；编辑账单 · Edit Screen</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>yyyy年M月d日 EEE</t>
+          <t>此账本已归档，无法修改</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Detail Screen</t>
+          <t>Detail Screen；编辑账单 · Edit Screen</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>修改</t>
+          <t>这笔记录已被删除</t>
         </is>
       </c>
       <c r="F83" s="5" t="n"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Detail Screen</t>
+          <t>Fields Card</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>记录详情</t>
+          <t>转入</t>
         </is>
       </c>
       <c r="F84" s="5" t="n"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Detail Screen；编辑账单 · Edit Screen</t>
+          <t>Fields Card</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>这个账本已归档，不能再修改记录。需要改动就先在「账本管理」里取消归档。</t>
+          <t>转出</t>
         </is>
       </c>
       <c r="F85" s="5" t="n"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Detail Screen；编辑账单 · Edit Screen</t>
+          <t>Fields Card；编辑账单 · Edit Screen</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>这笔记录已经不存在了</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="F86" s="5" t="n"/>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Fields Card</t>
+          <t>Fields Card；编辑账单 · Edit Screen；记账页 · Note Field</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>转入</t>
+          <t>交易对象</t>
         </is>
       </c>
       <c r="F87" s="5" t="n"/>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Fields Card</t>
+          <t>Fields Card；编辑账单 · Edit Screen；记账页 · Note Field</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>转出</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="F88" s="5" t="n"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Fields Card；编辑账单 · Edit Screen</t>
+          <t>Source Label</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>CSV 导入</t>
         </is>
       </c>
       <c r="F89" s="5" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Fields Card；编辑账单 · Edit Screen；记账页 · Note Field</t>
+          <t>Source Label</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>交易对象</t>
+          <t>月付自动生成</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Fields Card；编辑账单 · Edit Screen；记账页 · Note Field</t>
+          <t>Source Label；导出与备份 · Source Label</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>微信导入</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Source Label</t>
+          <t>Source Label；导出与备份 · Source Label</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>CSV 导入</t>
+          <t>支付宝导入</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Source Label</t>
+          <t>Source Label；导出与备份 · Source Label；导入账单 · Source Label</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>月付自动生成</t>
+          <t>手动录入</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Source Label；导出与备份 · Source Label</t>
+          <t>Source Label；导出与备份 · Source Label；导入账单 · Source Label</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>微信导入</t>
+          <t>模板</t>
         </is>
       </c>
       <c r="F94" s="5" t="n"/>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Source Label；导出与备份 · Source Label</t>
+          <t>Timestamp Row；编辑账单 · Date Time Fields；记账页 · Date Time Dialog</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>支付宝导入</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Source Label；导出与备份 · Source Label；导入账单 · Source Label</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>手动录入</t>
+          <t>账户互转</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Source Label；导出与备份 · Source Label；导入账单 · Source Label</t>
+          <t>Title；首页 / 记账 · Transaction Row Item；导入账单 · Import Row Card 等5处</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -2980,33 +2980,33 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>模板</t>
+          <t>未分类</t>
         </is>
       </c>
       <c r="F97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n">
+      <c r="A98" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>账单详情</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>Timestamp Row；编辑账单 · Date Time Fields；记账页 · Date Time Dialog</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>时间</t>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>搜索</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Amount Label</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>不限</t>
         </is>
       </c>
       <c r="F98" s="5" t="n"/>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>账单详情</t>
+          <t>搜索</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Amount Range Dialog</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>账户互转</t>
+          <t>不低于</t>
         </is>
       </c>
       <c r="F99" s="5" t="n"/>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>账单详情</t>
+          <t>搜索</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Title；首页 / 记账 · Transaction Row Item；导入账单 · Import Row Card 等5处</t>
+          <t>Amount Range Dialog</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -3058,33 +3058,33 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>不高于</t>
         </is>
       </c>
       <c r="F100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>搜索</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Amount Label</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>不限</t>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Amount Range Dialog</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>留空即不限制上限或下限</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>不低于</t>
+          <t>金额区间</t>
         </is>
       </c>
       <c r="F102" s="5" t="n"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Amount Range Dialog</t>
+          <t>Amount Range Dialog；统计 · Category Filter Dialog；通用界面组件 · Calendar Picker Dialog 等4处</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>不高于</t>
+          <t>确定</t>
         </is>
       </c>
       <c r="F103" s="5" t="n"/>
@@ -3152,17 +3152,17 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Amount Range Dialog</t>
+          <t>Clear Chip</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>留空即不限制这一端。</t>
+          <t>清除</t>
         </is>
       </c>
       <c r="F104" s="5" t="n"/>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Amount Range Dialog</t>
+          <t>Search Screen</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>金额区间</t>
+          <t xml:space="preserve"> · 合计 {Money.formatWithSymbol(state.totalCents)}</t>
         </is>
       </c>
       <c r="F105" s="5" t="n"/>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Amount Range Dialog；统计 · Category Filter Dialog；通用界面组件 · Calendar Picker Dialog 等4处</t>
+          <t>Search Screen</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>确定</t>
+          <t>交易对象或备注</t>
         </is>
       </c>
       <c r="F106" s="5" t="n"/>
@@ -3230,17 +3230,17 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Clear Chip</t>
+          <t>Search Screen</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>清除</t>
+          <t>全部 {state.resultCount} 条</t>
         </is>
       </c>
       <c r="F107" s="5" t="n"/>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · 合计 {Money.formatWithSymbol(state.totalCents)}</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="F108" s="5" t="n"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>交易对象或备注</t>
+          <t>开始</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -3313,12 +3313,12 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>收支</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>全部 {state.resultCount} 条</t>
+          <t>此账本暂无记录</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>没有符合条件的记录</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>开始</t>
+          <t>清空条件</t>
         </is>
       </c>
       <c r="F113" s="5" t="n"/>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>收支</t>
+          <t>筛选出 {state.resultCount} 条</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>没有符合条件的记录</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>清空条件</t>
+          <t>结束</t>
         </is>
       </c>
       <c r="F116" s="5" t="n"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Search Screen</t>
+          <t>Search Screen；统计；统计 · Resolve Range</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>筛选出 {state.resultCount} 条</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="F117" s="5" t="n"/>
@@ -3516,43 +3516,43 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Search Screen</t>
+          <t>Search Screen；设置 · FEATURES</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>搜索</t>
         </is>
       </c>
       <c r="F118" s="5" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="n">
+      <c r="A119" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>搜索</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>Search Screen</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>结束</t>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>统计</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Category Filter Dialog</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>未选择任何类别</t>
         </is>
       </c>
       <c r="F119" s="5" t="n"/>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>搜索</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>Search Screen</t>
+          <t>Category Filter Dialog</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>这个账本还没有记录</t>
+          <t>筛选类别</t>
         </is>
       </c>
       <c r="F120" s="5" t="n"/>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>搜索</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>Search Screen；设置 · FEATURES</t>
+          <t>Category Rank Row</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
@@ -3604,33 +3604,33 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>搜索</t>
+          <t>{(rank.share * 100).toInt()}%</t>
         </is>
       </c>
       <c r="F121" s="5" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>统计</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>Category Filter Dialog</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>一个类别都没选，统计会是空的。</t>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Donut Card</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>支出构成</t>
         </is>
       </c>
       <c r="F122" s="5" t="n"/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Category Filter Dialog</t>
+          <t>Filter Button</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>筛选类别</t>
+          <t>筛选</t>
         </is>
       </c>
       <c r="F123" s="5" t="n"/>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Category Rank Row</t>
+          <t>Legend Row</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>{(rank.share * 100).toInt()}%</t>
+          <t>{(slice.share * 100).toInt()}%</t>
         </is>
       </c>
       <c r="F124" s="5" t="n"/>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Donut Card</t>
+          <t>Resolve Range</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>支出构成</t>
+          <t>{today.year} 年</t>
         </is>
       </c>
       <c r="F125" s="5" t="n"/>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Filter Button</t>
+          <t>Resolve Range</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>筛选</t>
+          <t>近 30 天</t>
         </is>
       </c>
       <c r="F126" s="5" t="n"/>
@@ -3750,17 +3750,17 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Legend Row</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>{(slice.share * 100).toInt()}%</t>
+          <t>大类</t>
         </is>
       </c>
       <c r="F127" s="5" t="n"/>
@@ -3776,17 +3776,17 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Resolve Range</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>{today.year} 年</t>
+          <t>小类</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Resolve Range</t>
+          <t>Stats Screen</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>近 30 天</t>
+          <t>支出排行</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -3828,17 +3828,17 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Stats Screen</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>大类</t>
+          <t>这段时间暂无支出记录</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -3854,17 +3854,17 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Term Picker</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>小类</t>
+          <t>在「我的 → 学期设置」添加一个日期区间以查看学期总账</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Stats Screen</t>
+          <t>Term Picker</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>支出排行</t>
+          <t>暂未设置学期</t>
         </is>
       </c>
       <c r="F132" s="5" t="n"/>
@@ -3906,17 +3906,17 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Stats Screen</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>这段时间还没有支出记录</t>
+          <t>今年</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -3932,17 +3932,17 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>Term Picker</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>去「我的 → 学期设置」添加一个日期区间（比如 2026 秋季学期：9月1日 到 1月15日），这里就能按学期看总账了。</t>
+          <t>学期</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -3958,43 +3958,43 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Term Picker</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>还没有设置学期</t>
+          <t>近30天</t>
         </is>
       </c>
       <c r="F135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="n">
+      <c r="A136" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>统计</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
-          <t>统计</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>选项名称</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>今年</t>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>账户</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>ACCOUNT_TYPES；Account Type Label</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>信用卡</t>
         </is>
       </c>
       <c r="F136" s="5" t="n"/>
@@ -4005,22 +4005,22 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>账户</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>ACCOUNT_TYPES；Account Type Label</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>学期</t>
+          <t>储值卡</t>
         </is>
       </c>
       <c r="F137" s="5" t="n"/>
@@ -4031,48 +4031,48 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>账户</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>ACCOUNT_TYPES；Account Type Label</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>近30天</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F138" s="5" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>账户</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>ACCOUNT_TYPES；Account Type Label</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>信用卡</t>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>ACCOUNT_TYPES；Account Type Label</t>
+          <t>Account Editor Dialog</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>储值卡</t>
+          <t>「{target.name}」会从账户列表移除，已有的流水仍然保留。</t>
         </is>
       </c>
       <c r="F140" s="5" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>ACCOUNT_TYPES；Account Type Label</t>
+          <t>Account Editor Dialog</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>余额</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -4140,17 +4140,17 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>ACCOUNT_TYPES；Account Type Label</t>
+          <t>Account Editor Dialog</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>删除账户</t>
         </is>
       </c>
       <c r="F142" s="5" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>「{target.name}」会从账户列表移除，已有的流水仍然保留。</t>
+          <t>注销的卡可以关掉，流水仍保留。</t>
         </is>
       </c>
       <c r="F143" s="5" t="n"/>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>添加账户</t>
         </is>
       </c>
       <c r="F144" s="5" t="n"/>
@@ -4223,12 +4223,12 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>删除账户</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="F145" s="5" t="n"/>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>改了就按新余额继续记账，之前的流水不会变。</t>
+          <t>编辑账户</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>注销的卡可以关掉，流水仍保留。</t>
+          <t>计入总资产</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>添加账户</t>
+          <t>记账从这里开始累加。</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>账单日</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>编辑账户</t>
+          <t>额度（可留空）</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog</t>
+          <t>Account Editor Dialog；类别管理 · Category Editor Dialog</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>计入总资产</t>
+          <t>颜色</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog</t>
+          <t>Account Editor Dialog；类别管理 · Category Editor Dialog；记账页 · Monthly Panel 等6处</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>记账从这里开始累加。</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -4426,17 +4426,17 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog</t>
+          <t>Account Editor Dialog；类别管理 · Group Header；编辑账单 · Edit Header 等5处</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>账单日</t>
+          <t>删除</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog</t>
+          <t>Account Editor Dialog；记账页 · Monthly Panel；月付 / 分期 · Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>额度（可留空）</t>
+          <t>还款日</t>
         </is>
       </c>
       <c r="F154" s="5" t="n"/>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog；类别管理 · Category Editor Dialog</t>
+          <t>Account Editor Dialog；预算 · Add Leaf Button；预算 · Budget Editor Dialog 等15处</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>颜色</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="F155" s="5" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog；类别管理 · Category Editor Dialog；记账页 · Monthly Panel 等6处</t>
+          <t>Account Editor Dialog；预算 · Budget Editor Dialog；类别管理 · Category Editor Dialog 等8处</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>保存</t>
         </is>
       </c>
       <c r="F156" s="5" t="n"/>
@@ -4530,17 +4530,17 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog；类别管理 · Group Header；编辑账单 · Edit Header 等5处</t>
+          <t>Account Subtitle</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>删除</t>
+          <t>{typeLabel} · 不计入总资产</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog；记账页 · Monthly Panel；月付 / 分期 · Installment Editor Dialog</t>
+          <t>Account Subtitle</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>还款日</t>
+          <t>{typeLabel} · 每月 {account.repayDay} 日还款</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog；预算 · Add Leaf Button；预算 · Budget Editor Dialog 等15处</t>
+          <t>Accounts Screen</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>当前账本是累计模式</t>
         </is>
       </c>
       <c r="F159" s="5" t="n"/>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>Account Editor Dialog；预算 · Budget Editor Dialog；类别管理 · Category Editor Dialog 等8处</t>
+          <t>Accounts Screen</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>保存</t>
+          <t>累计模式只记录收支，不涉及账户。需要账户和余额，请切换到预算模式账本。</t>
         </is>
       </c>
       <c r="F160" s="5" t="n"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>Account Subtitle</t>
+          <t>Accounts Screen</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>{typeLabel} · 不计入总资产</t>
+          <t>还没有账户，点右上角「添加」建一个</t>
         </is>
       </c>
       <c r="F161" s="5" t="n"/>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>Account Subtitle</t>
+          <t>Accounts Screen；类别管理 · Group Header；设置 · Term Settings Screen</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>{typeLabel} · 每月 {account.repayDay} 日还款</t>
+          <t>添加</t>
         </is>
       </c>
       <c r="F162" s="5" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>Accounts Screen</t>
+          <t>Accounts Screen；账单详情 · Fields Card；编辑账单 · Edit Screen 等6处</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>当前账本是累计模式</t>
+          <t>账户</t>
         </is>
       </c>
       <c r="F163" s="5" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>Accounts Screen</t>
+          <t>Accounts Screen；首页 / 记账 · Ledger Chip；设置 · FEATURES 等4处</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>累计模式只记录收支，不涉及账户。需要账户和余额，请切换到预算模式账本。</t>
+          <t>账本</t>
         </is>
       </c>
       <c r="F164" s="5" t="n"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>Accounts Screen</t>
+          <t>Net Worth Card</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>还没有账户，点右上角「添加」建一个</t>
+          <t>净资产</t>
         </is>
       </c>
       <c r="F165" s="5" t="n"/>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>Accounts Screen；类别管理 · Group Header；设置 · Term Settings Screen</t>
+          <t>Quick Amount Row；预算 · Budget Editor Dialog</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
@@ -4774,33 +4774,33 @@
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>添加</t>
+          <t>+{yuan}</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="n">
+      <c r="A167" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>账户</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>Accounts Screen；账单详情 · Fields Card；编辑账单 · Edit Screen 等6处</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>账户</t>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>预算</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Add Leaf Button</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>添加类别预算</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>Accounts Screen；首页 / 记账 · Ledger Chip；设置 · FEATURES 等4处</t>
+          <t>Add Leaf Button</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>账本</t>
+          <t>选择类别</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>Net Worth Card</t>
+          <t>Back Chip；类别管理 · Back Chip；账单详情 · Detail Screen 等11处</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>净资产</t>
+          <t>‹</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>Net Worth Card</t>
+          <t>Budget Editor Dialog</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>负债</t>
+          <t>{row.name} 预算</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>Net Worth Card</t>
+          <t>Budget Editor Dialog</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>资产</t>
+          <t>上限</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>Quick Amount Row；预算 · Budget Editor Dialog</t>
+          <t>Budget Editor Dialog</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t>+{yuan}</t>
+          <t xml:space="preserve">本月已花 </t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>账户</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>Stat Pill</t>
+          <t>Budget Editor Dialog</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
@@ -4956,33 +4956,33 @@
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>{label} {amount}</t>
+          <t>留空或填 0 表示取消。与[明细]页预算同步。</t>
         </is>
       </c>
       <c r="F173" s="5" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n">
+      <c r="A174" s="6" t="n">
         <v>171</v>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
         <is>
           <t>预算</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>Add Leaf Button</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>添加类别预算</t>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>Budget Editor Dialog</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>留空或填 0 表示取消这个预算。</t>
         </is>
       </c>
       <c r="F174" s="5" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>Add Leaf Button</t>
+          <t>Budget Row Card</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>选择类别</t>
+          <t>接近上限</t>
         </is>
       </c>
       <c r="F175" s="5" t="n"/>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>Back Chip；类别管理 · Back Chip；账单详情 · Detail Screen 等11处</t>
+          <t>Budget Row Card</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>‹</t>
+          <t>超支</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Budget Editor Dialog</t>
+          <t>Budget Settings Screen</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>{row.name} 预算</t>
+          <t>单独设限的类别</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Budget Editor Dialog</t>
+          <t>Budget Settings Screen</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>上限</t>
+          <t>各大类</t>
         </is>
       </c>
       <c r="F178" s="5" t="n"/>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>Budget Editor Dialog</t>
+          <t>Budget Settings Screen</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">本月已花 </t>
+          <t>没有单独设限的类别。</t>
         </is>
       </c>
       <c r="F179" s="5" t="n"/>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>Budget Editor Dialog</t>
+          <t>Budget Settings Screen；设置 · Ledger Card</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>留空或填 0 表示取消。这个数字和明细页生活费卡片上的额度是同一个，在任意一边改都会同步。</t>
+          <t>预算</t>
         </is>
       </c>
       <c r="F180" s="5" t="n"/>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>Budget Editor Dialog</t>
+          <t>Total Budget Card</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>留空或填 0 表示取消这个预算。</t>
+          <t xml:space="preserve">已花 </t>
         </is>
       </c>
       <c r="F181" s="5" t="n"/>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>Budget Row Card</t>
+          <t>Total Budget Card</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>接近上限</t>
+          <t xml:space="preserve">已超 </t>
         </is>
       </c>
       <c r="F182" s="5" t="n"/>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>Budget Row Card</t>
+          <t>Total Budget Card</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>超支</t>
+          <t>点这里设一个月度上限（与[明细]页生活费同步）</t>
         </is>
       </c>
       <c r="F183" s="5" t="n"/>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>Budget Settings Screen</t>
+          <t>Total Budget Card</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>单独设限的类别</t>
+          <t xml:space="preserve">还剩 </t>
         </is>
       </c>
       <c r="F184" s="5" t="n"/>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>Budget Settings Screen</t>
+          <t>Total Budget Card；Budget Editor Dialog；Month Stream</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
@@ -5268,33 +5268,33 @@
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>各大类</t>
+          <t>本月总预算</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="n">
+      <c r="A186" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>预算</t>
-        </is>
-      </c>
-      <c r="C186" s="7" t="inlineStr">
-        <is>
-          <t>Budget Settings Screen</t>
-        </is>
-      </c>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>没有单独设限的类别。大类预算已覆盖的，不必再设一层。</t>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>月付 / 分期</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Date Pick Field</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>{label}　{DateLabels.dayLabel(dateKey)}</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -5305,22 +5305,22 @@
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>月付 / 分期</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>Budget Settings Screen；设置 · Ledger Card</t>
+          <t>Date Pick Field；设置 · Date Field</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>选择{label}</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>月付 / 分期</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>Total Budget Card</t>
+          <t>Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">已花 </t>
+          <t>与首次扣款同时一次性收取。</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -5357,12 +5357,12 @@
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>月付 / 分期</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>Total Budget Card</t>
+          <t>Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">已超 </t>
+          <t>关联账户</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>月付 / 分期</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>Total Budget Card</t>
+          <t>Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>点这里设一个月度上限（与明细页生活费同步）</t>
+          <t>恢复此计划</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>月付 / 分期</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>Total Budget Card</t>
+          <t>Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">还剩 </t>
+          <t>新建月付</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>预算</t>
+          <t>月付 / 分期</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>Total Budget Card；Budget Editor Dialog；Month Stream</t>
+          <t>Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
@@ -5450,33 +5450,33 @@
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>本月总预算</t>
+          <t>每期约 {Money.formatWithSymbol(perPeriod)}</t>
         </is>
       </c>
       <c r="F192" s="5" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n">
+      <c r="A193" s="6" t="n">
         <v>190</v>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B193" s="7" t="inlineStr">
         <is>
           <t>月付 / 分期</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>Date Pick Field</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>{label}　{DateLabels.dayLabel(dateKey)}</t>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>Installment Editor Dialog</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>终止此计划</t>
         </is>
       </c>
       <c r="F193" s="5" t="n"/>
@@ -5492,17 +5492,17 @@
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>Date Pick Field；设置 · Date Field</t>
+          <t>Installment Editor Dialog</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
-          <t>选择{label}</t>
+          <t>编辑月付</t>
         </is>
       </c>
       <c r="F194" s="5" t="n"/>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>一次性收取，和第一期一起扣。</t>
+          <t>起始日期</t>
         </is>
       </c>
       <c r="F195" s="5" t="n"/>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>关联账户</t>
+          <t>，最后一期在 {it}</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Installment Settings Screen</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>恢复此计划</t>
+          <t>管理已添加的[月付]条目，进行添加、删除或编辑</t>
         </is>
       </c>
       <c r="F197" s="5" t="n"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Installment Settings Screen</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>新建月付</t>
+          <t>还没有计划，点右上角「新建」加一个</t>
         </is>
       </c>
       <c r="F198" s="5" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Installment Settings Screen；设置 · Ledger Settings Screen</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>每期约 {Money.formatWithSymbol(perPeriod)}</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="F199" s="5" t="n"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Installment Settings Screen；设置 · Settings Screen</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>终止只影响之后的扣款，已经记下的账目不动。</t>
+          <t>月付管理</t>
         </is>
       </c>
       <c r="F200" s="5" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>终止此计划</t>
+          <t xml:space="preserve"> · 已终止</t>
         </is>
       </c>
       <c r="F201" s="5" t="n"/>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C202" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D202" s="7" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="E202" s="7" t="inlineStr">
         <is>
-          <t>编辑月付</t>
+          <t>下次 {DateKeys.parseDateKey(it)}</t>
         </is>
       </c>
       <c r="F202" s="5" t="n"/>
@@ -5726,17 +5726,17 @@
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>起始日期</t>
+          <t>共 {Money.formatCompact(plan.totalAmountCents)}</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>Installment Editor Dialog</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D204" s="7" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>，最后一期在 {it}</t>
+          <t>已还 {row.paidPeriods}/{plan.periodCount} 期</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Installment Settings Screen</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>管理已添加的【月付】条目，进行添加、删除或编辑</t>
+          <t>已还完</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="C206" s="7" t="inlineStr">
         <is>
-          <t>Installment Settings Screen</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D206" s="7" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>还没有计划，点右上角「新建」加一个</t>
+          <t>未还</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>Installment Settings Screen；设置 · Ledger Settings Screen</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>每月 {plan.repayDay} 日</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C208" s="7" t="inlineStr">
         <is>
-          <t>Installment Settings Screen；设置 · Settings Screen</t>
+          <t>Plan Card</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
@@ -5866,33 +5866,33 @@
       </c>
       <c r="E208" s="7" t="inlineStr">
         <is>
-          <t>月付管理</t>
+          <t>每期 {Money.formatWithSymbol(InstallmentSchedule.amountForPeriod(plan.totalAmountCents, plan.periodCount, 1))} · 每月 {plan.repayDay} 日</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="6" t="n">
+      <c r="A209" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="B209" s="7" t="inlineStr">
-        <is>
-          <t>月付 / 分期</t>
-        </is>
-      </c>
-      <c r="C209" s="7" t="inlineStr">
-        <is>
-          <t>Plan Card</t>
-        </is>
-      </c>
-      <c r="D209" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E209" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> · 已终止</t>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>类别管理</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>Category Editor Dialog</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>「{existing.name}」会被删除，已经记在它下面的条目会变成未分类。</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -5903,22 +5903,22 @@
       </c>
       <c r="B210" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Editor Dialog</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>下次 {DateKeys.parseDateKey(it)}</t>
+          <t>删除类别</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -5929,22 +5929,22 @@
       </c>
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Editor Dialog</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>共 {Money.formatCompact(plan.totalAmountCents)}</t>
+          <t>删除这个类别</t>
         </is>
       </c>
       <c r="F211" s="5" t="n"/>
@@ -5955,12 +5955,12 @@
       </c>
       <c r="B212" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Editor Dialog</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>已还 {row.paidPeriods}/{plan.periodCount} 期</t>
+          <t>图标</t>
         </is>
       </c>
       <c r="F212" s="5" t="n"/>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="B213" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Editor Dialog</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>已还完</t>
+          <t>归属大类</t>
         </is>
       </c>
       <c r="F213" s="5" t="n"/>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Editor Dialog</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>未还</t>
+          <t>添加类别</t>
         </is>
       </c>
       <c r="F214" s="5" t="n"/>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Editor Dialog</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>每月 {plan.repayDay} 日</t>
+          <t>编辑类别</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="B216" s="7" t="inlineStr">
         <is>
-          <t>月付 / 分期</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>Plan Card</t>
+          <t>Category Row</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
@@ -6074,33 +6074,33 @@
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>每期 {Money.formatWithSymbol(InstallmentSchedule.amountForPeriod(plan.totalAmountCents, plan.periodCount, 1))} · 每月 {plan.repayDay} 日</t>
+          <t>内置</t>
         </is>
       </c>
       <c r="F216" s="5" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n">
+      <c r="A217" s="6" t="n">
         <v>214</v>
       </c>
-      <c r="B217" s="4" t="inlineStr">
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t>类别管理</t>
         </is>
       </c>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>Category Editor Dialog</t>
-        </is>
-      </c>
-      <c r="D217" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>「{existing.name}」会被删除，已经记在它下面的条目会变成未分类。</t>
+      <c r="C217" s="7" t="inlineStr">
+        <is>
+          <t>Category Settings Screen</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>加类别</t>
         </is>
       </c>
       <c r="F217" s="5" t="n"/>
@@ -6116,17 +6116,17 @@
       </c>
       <c r="C218" s="7" t="inlineStr">
         <is>
-          <t>Category Editor Dialog</t>
+          <t>Category Settings Screen；Category Editor Dialog</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>删除类别</t>
+          <t>添加大类</t>
         </is>
       </c>
       <c r="F218" s="5" t="n"/>
@@ -6142,17 +6142,17 @@
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>Category Editor Dialog</t>
+          <t>Category Settings Screen；编辑账单 · Type Row；记账页 等9处</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>删除这个类别</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C220" s="7" t="inlineStr">
         <is>
-          <t>Category Editor Dialog</t>
+          <t>Category Settings Screen；编辑账单 · Type Row；记账页 等9处</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="F220" s="5" t="n"/>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>Category Editor Dialog</t>
+          <t>Category Settings Screen；设置 · FEATURES；设置 · Settings Screen</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
@@ -6204,33 +6204,33 @@
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>归属大类</t>
+          <t>类别管理</t>
         </is>
       </c>
       <c r="F221" s="5" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="6" t="n">
+      <c r="A222" s="3" t="n">
         <v>219</v>
       </c>
-      <c r="B222" s="7" t="inlineStr">
-        <is>
-          <t>类别管理</t>
-        </is>
-      </c>
-      <c r="C222" s="7" t="inlineStr">
-        <is>
-          <t>Category Editor Dialog</t>
-        </is>
-      </c>
-      <c r="D222" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E222" s="7" t="inlineStr">
-        <is>
-          <t>本身就是大类</t>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>导入账单</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Account Picker</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>当前账本没有可用账户，先在账户页建一个。</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -6241,12 +6241,12 @@
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>Category Editor Dialog</t>
+          <t>Account Picker</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>添加类别</t>
+          <t>累计模式的账本无账户功能。</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -6267,12 +6267,12 @@
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>Category Editor Dialog</t>
+          <t>Account Picker</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>编辑类别</t>
+          <t>记入账户</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>Category Row</t>
+          <t>Batch Card</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>内置</t>
+          <t xml:space="preserve"> · 跳过 {batch.batch.skippedCount} 条</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
         <is>
-          <t>Category Settings Screen</t>
+          <t>Batch Card</t>
         </is>
       </c>
       <c r="D226" s="7" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>加类别</t>
+          <t>{batch.batch.txnCount} 条</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -6345,22 +6345,22 @@
       </c>
       <c r="B227" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
         <is>
-          <t>Category Settings Screen；Category Editor Dialog</t>
+          <t>Batch Card</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>添加大类</t>
+          <t>撤销</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="B228" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>Category Settings Screen；编辑账单 · Type Row；记账页 等9处</t>
+          <t>Category Drop Target</t>
         </is>
       </c>
       <c r="D228" s="7" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>{name} ▾</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -6397,22 +6397,22 @@
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>Category Settings Screen；编辑账单 · Type Row；记账页 等9处</t>
+          <t>Commit Import</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>提示消息</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>已导入 {selected.size} 条记录，可在下方撤销。</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="B230" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
         <is>
-          <t>Category Settings Screen；设置 · FEATURES；设置 · Settings Screen</t>
+          <t>Import Row Card</t>
         </is>
       </c>
       <c r="D230" s="7" t="inlineStr">
@@ -6438,33 +6438,33 @@
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>类别管理</t>
+          <t>已导入过</t>
         </is>
       </c>
       <c r="F230" s="5" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="n">
+      <c r="A231" s="6" t="n">
         <v>228</v>
       </c>
-      <c r="B231" s="4" t="inlineStr">
+      <c r="B231" s="7" t="inlineStr">
         <is>
           <t>导入账单</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>Account Picker</t>
-        </is>
-      </c>
-      <c r="D231" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>当前账本没有可用账户，先在账户页建一个。</t>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>Import Row Card</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>未命名记录</t>
         </is>
       </c>
       <c r="F231" s="5" t="n"/>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>Account Picker</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D232" s="7" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>累计模式的账本不记账户，记录会记入它自己的内部账户。</t>
+          <t>导入 {state.selected.size} 条 · 支出 {state.selectedExpenseCount} / 收入 {state.selectedIncomeCount}</t>
         </is>
       </c>
       <c r="F232" s="5" t="n"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C233" s="7" t="inlineStr">
         <is>
-          <t>Account Picker</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>记入账户</t>
+          <t>导入中…</t>
         </is>
       </c>
       <c r="F233" s="5" t="n"/>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>Batch Card</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D234" s="7" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · 跳过 {batch.batch.skippedCount} 条</t>
+          <t>导入记录</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>Batch Card</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>{batch.batch.txnCount} 条</t>
+          <t>读取中…</t>
         </is>
       </c>
       <c r="F235" s="5" t="n"/>
@@ -6584,17 +6584,17 @@
       </c>
       <c r="C236" s="7" t="inlineStr">
         <is>
-          <t>Batch Card</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>撤销</t>
+          <t>账单.csv</t>
         </is>
       </c>
       <c r="F236" s="5" t="n"/>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="C237" s="7" t="inlineStr">
         <is>
-          <t>Category Drop Target</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D237" s="7" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>{name} ▾</t>
+          <t>还没有导入过账单。</t>
         </is>
       </c>
       <c r="F237" s="5" t="n"/>
@@ -6636,17 +6636,17 @@
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>Commit Import</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>提示消息</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>已导入 {selected.size} 条记录，可在下方撤销。</t>
+          <t>选择账单文件</t>
         </is>
       </c>
       <c r="F238" s="5" t="n"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="C239" s="7" t="inlineStr">
         <is>
-          <t>Import Row Card</t>
+          <t>Import Screen</t>
         </is>
       </c>
       <c r="D239" s="7" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>已导入过</t>
+          <t>重新选择文件</t>
         </is>
       </c>
       <c r="F239" s="5" t="n"/>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="C240" s="7" t="inlineStr">
         <is>
-          <t>Import Row Card</t>
+          <t>Import Screen；统计 · Category Filter Dialog</t>
         </is>
       </c>
       <c r="D240" s="7" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>未命名记录</t>
+          <t>全不选</t>
         </is>
       </c>
       <c r="F240" s="5" t="n"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Import Screen；统计 · Category Filter Dialog</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>导入 {state.selected.size} 条 · 支出 {state.selectedExpenseCount} / 收入 {state.selectedIncomeCount}</t>
+          <t>全选</t>
         </is>
       </c>
       <c r="F241" s="5" t="n"/>
@@ -6740,17 +6740,17 @@
       </c>
       <c r="C242" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Import Screen；设置 · FEATURES；设置 · Settings Screen</t>
         </is>
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>导入中…</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C243" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Inferred Notice</t>
         </is>
       </c>
       <c r="D243" s="7" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>导入记录</t>
+          <t>全部改为支出</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C244" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Inferred Notice</t>
         </is>
       </c>
       <c r="D244" s="7" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>读取中…</t>
+          <t>全部改为收入</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="C245" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Inferred Notice</t>
         </is>
       </c>
       <c r="D245" s="7" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>账单.csv</t>
+          <t>这个文件没有「收/支」列，{count} 条的收支方向为预测得出。</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C246" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Intro Card</t>
         </is>
       </c>
       <c r="D246" s="7" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>还没有导入过账单。</t>
+          <t>支持微信、支付宝导出的账单（CSV 或 xlsx），以及本应用导出的 CSV。</t>
         </is>
       </c>
       <c r="F246" s="5" t="n"/>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="C247" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Ledger Picker</t>
         </is>
       </c>
       <c r="D247" s="7" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>选择账单文件</t>
+          <t xml:space="preserve"> · 累计</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="C248" s="7" t="inlineStr">
         <is>
-          <t>Import Screen</t>
+          <t>Ledger Picker</t>
         </is>
       </c>
       <c r="D248" s="7" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>重新选择文件</t>
+          <t xml:space="preserve"> ▾</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="C249" s="7" t="inlineStr">
         <is>
-          <t>Import Screen；统计 · Category Filter Dialog</t>
+          <t>Ledger Picker</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>全不选</t>
+          <t>{ledger.name} · 累计</t>
         </is>
       </c>
       <c r="F249" s="5" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C250" s="7" t="inlineStr">
         <is>
-          <t>Import Screen；统计 · Category Filter Dialog</t>
+          <t>Ledger Picker</t>
         </is>
       </c>
       <c r="D250" s="7" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>全选</t>
+          <t>导入到账本</t>
         </is>
       </c>
       <c r="F250" s="5" t="n"/>
@@ -6974,17 +6974,17 @@
       </c>
       <c r="C251" s="7" t="inlineStr">
         <is>
-          <t>Import Screen；设置 · FEATURES；设置 · Settings Screen</t>
+          <t>Ledger Picker</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>没有可用的账本</t>
         </is>
       </c>
       <c r="F251" s="5" t="n"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="C252" s="7" t="inlineStr">
         <is>
-          <t>Inferred Notice</t>
+          <t>On File Picked</t>
         </is>
       </c>
       <c r="D252" s="7" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>全部改为支出</t>
+          <t>没有读到可导入的记录，确认这是微信或支付宝导出的账单（CSV 或 xlsx）。</t>
         </is>
       </c>
       <c r="F252" s="5" t="n"/>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>Inferred Notice</t>
+          <t>Review Summary</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>全部改为收入</t>
+          <t>{state.duplicateCount} 条已存在</t>
         </is>
       </c>
       <c r="F253" s="5" t="n"/>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="C254" s="7" t="inlineStr">
         <is>
-          <t>Inferred Notice</t>
+          <t>Review Summary</t>
         </is>
       </c>
       <c r="D254" s="7" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>点每条右侧的「支出/收入」可以单独改；如果整体反了，用下面的按钮一次改完。</t>
+          <t>{state.skippedCount} 条已跳过</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="C255" s="7" t="inlineStr">
         <is>
-          <t>Inferred Notice</t>
+          <t>Review Summary</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>这个文件没有「收/支」列，{count} 条的收支方向是推测出来的。</t>
+          <t>共 {state.rows.size} 条</t>
         </is>
       </c>
       <c r="F255" s="5" t="n"/>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="C256" s="7" t="inlineStr">
         <is>
-          <t>Intro Card</t>
+          <t>Review Summary</t>
         </is>
       </c>
       <c r="D256" s="7" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>支持微信、支付宝导出的账单（CSV 或 xlsx），以及本应用导出的 CSV。</t>
+          <t>此文件里的记录已被全部导入。</t>
         </is>
       </c>
       <c r="F256" s="5" t="n"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C257" s="7" t="inlineStr">
         <is>
-          <t>Ledger Picker</t>
+          <t>Review Summary；Source Label</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · 累计</t>
+          <t>CSV 文件</t>
         </is>
       </c>
       <c r="F257" s="5" t="n"/>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="C258" s="7" t="inlineStr">
         <is>
-          <t>Ledger Picker</t>
+          <t>Source Label</t>
         </is>
       </c>
       <c r="D258" s="7" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ▾</t>
+          <t>微信账单</t>
         </is>
       </c>
       <c r="F258" s="5" t="n"/>
@@ -7182,17 +7182,17 @@
       </c>
       <c r="C259" s="7" t="inlineStr">
         <is>
-          <t>Ledger Picker</t>
+          <t>Undo Import</t>
         </is>
       </c>
       <c r="D259" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>提示消息</t>
         </is>
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>{ledger.name} · 累计</t>
+          <t>已撤销这次导入的记录。</t>
         </is>
       </c>
       <c r="F259" s="5" t="n"/>
@@ -7208,17 +7208,17 @@
       </c>
       <c r="C260" s="7" t="inlineStr">
         <is>
-          <t>Ledger Picker</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="D260" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>导入到账本</t>
+          <t>微信支付账单</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -7234,17 +7234,17 @@
       </c>
       <c r="C261" s="7" t="inlineStr">
         <is>
-          <t>Ledger Picker</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>没有可用的账本</t>
+          <t>本应用导出的文件</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -7260,17 +7260,17 @@
       </c>
       <c r="C262" s="7" t="inlineStr">
         <is>
-          <t>On File Picked</t>
+          <t>导入账单</t>
         </is>
       </c>
       <c r="D262" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E262" s="7" t="inlineStr">
         <is>
-          <t>没有读到可导入的记录，确认这是微信或支付宝导出的账单（CSV 或 xlsx）。</t>
+          <t>通用 CSV</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -7286,43 +7286,43 @@
       </c>
       <c r="C263" s="7" t="inlineStr">
         <is>
-          <t>Review Summary</t>
+          <t>导入账单；Source Label</t>
         </is>
       </c>
       <c r="D263" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>{state.duplicateCount} 条已存在</t>
+          <t>支付宝账单</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="n">
+      <c r="A264" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="B264" s="7" t="inlineStr">
-        <is>
-          <t>导入账单</t>
-        </is>
-      </c>
-      <c r="C264" s="7" t="inlineStr">
-        <is>
-          <t>Review Summary</t>
-        </is>
-      </c>
-      <c r="D264" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E264" s="7" t="inlineStr">
-        <is>
-          <t>{state.skippedCount} 条已跳过</t>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>导出与备份</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Confirm Restore</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>已恢复：{file.rowCount} 条数据</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
         <is>
-          <t>Review Summary</t>
+          <t>Confirm Restore</t>
         </is>
       </c>
       <c r="D265" s="7" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>共 {state.rows.size} 条</t>
+          <t>恢复失败，数据没有被改动。</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -7359,12 +7359,12 @@
       </c>
       <c r="B266" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
         <is>
-          <t>Review Summary</t>
+          <t>Export Option</t>
         </is>
       </c>
       <c r="D266" s="7" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>这个文件里的记录都已经在账本里了。</t>
+          <t>{scope.detail} · 共 {count} 条</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -7385,22 +7385,22 @@
       </c>
       <c r="B267" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>Review Summary；Source Label</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D267" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>CSV 文件</t>
+          <t>从备份文件恢复</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B268" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C268" s="7" t="inlineStr">
         <is>
-          <t>Source Label</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D268" s="7" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>微信账单</t>
+          <t>保存为 .{AppBackup.EXTENSION} 文件，供恢复数据用。</t>
         </is>
       </c>
       <c r="F268" s="5" t="n"/>
@@ -7437,22 +7437,22 @@
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
         <is>
-          <t>Undo Import</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D269" s="7" t="inlineStr">
         <is>
-          <t>提示消息</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
         <is>
-          <t>已撤销这次导入的记录。</t>
+          <t>存储全部应用数据为备份文件，以供恢复数据用。</t>
         </is>
       </c>
       <c r="F269" s="5" t="n"/>
@@ -7463,22 +7463,22 @@
       </c>
       <c r="B270" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C270" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D270" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E270" s="7" t="inlineStr">
         <is>
-          <t>微信支付账单</t>
+          <t>导出备份文件</t>
         </is>
       </c>
       <c r="F270" s="5" t="n"/>
@@ -7489,22 +7489,22 @@
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D271" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr">
         <is>
-          <t>本应用导出的文件</t>
+          <t>导出所选账本为 CSV 文件。</t>
         </is>
       </c>
       <c r="F271" s="5" t="n"/>
@@ -7515,22 +7515,22 @@
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C272" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D272" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E272" s="7" t="inlineStr">
         <is>
-          <t>通用 CSV</t>
+          <t>导出账单</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -7541,48 +7541,48 @@
       </c>
       <c r="B273" s="7" t="inlineStr">
         <is>
-          <t>导入账单</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>导入账单；Source Label</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D273" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E273" s="7" t="inlineStr">
         <is>
-          <t>支付宝账单</t>
+          <t>已恢复</t>
         </is>
       </c>
       <c r="F273" s="5" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="n">
+      <c r="A274" s="6" t="n">
         <v>271</v>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B274" s="7" t="inlineStr">
         <is>
           <t>导出与备份</t>
         </is>
       </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>Confirm Restore</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E274" s="4" t="inlineStr">
-        <is>
-          <t>已恢复：{file.rowCount} 条数据</t>
+      <c r="C274" s="7" t="inlineStr">
+        <is>
+          <t>Export Screen</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="inlineStr">
+        <is>
+          <t>应用备份</t>
         </is>
       </c>
       <c r="F274" s="5" t="n"/>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C275" s="7" t="inlineStr">
         <is>
-          <t>Confirm Restore</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D275" s="7" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="E275" s="7" t="inlineStr">
         <is>
-          <t>恢复失败，数据没有被改动。</t>
+          <t>正在恢复，请不要退出…</t>
         </is>
       </c>
       <c r="F275" s="5" t="n"/>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="C276" s="7" t="inlineStr">
         <is>
-          <t>Export Option</t>
+          <t>Export Screen</t>
         </is>
       </c>
       <c r="D276" s="7" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E276" s="7" t="inlineStr">
         <is>
-          <t>{scope.detail} · 共 {count} 条</t>
+          <t>这个选择下还没有记录可导出。</t>
         </is>
       </c>
       <c r="F276" s="5" t="n"/>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="D277" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E277" s="7" t="inlineStr">
         <is>
-          <t>从备份文件恢复</t>
+          <t>选择之前导出的备份，用它覆盖当前的全部数据</t>
         </is>
       </c>
       <c r="F277" s="5" t="n"/>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C278" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Export Screen；On Backup Write Finished</t>
         </is>
       </c>
       <c r="D278" s="7" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="E278" s="7" t="inlineStr">
         <is>
-          <t>保存为 .{AppBackup.EXTENSION} 文件，可以拷到别的设备或云盘</t>
+          <t>备份已导出</t>
         </is>
       </c>
       <c r="F278" s="5" t="n"/>
@@ -7702,17 +7702,17 @@
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Export Screen；On Write Finished</t>
         </is>
       </c>
       <c r="D279" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E279" s="7" t="inlineStr">
         <is>
-          <t>导出备份文件</t>
+          <t>已导出</t>
         </is>
       </c>
       <c r="F279" s="5" t="n"/>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C280" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Export Screen；设置 · Settings Screen</t>
         </is>
       </c>
       <c r="D280" s="7" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>导出所选账本为 CSV 文件，可用表格软件打开；选「全部账本」时会多一列「账本」。</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -7754,17 +7754,17 @@
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>On Backup Write Finished</t>
         </is>
       </c>
       <c r="D281" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E281" s="7" t="inlineStr">
         <is>
-          <t>导出账单</t>
+          <t>备份导出失败，请换一个位置重试</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="C282" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>On Restore Read Failed</t>
         </is>
       </c>
       <c r="D282" s="7" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>已恢复</t>
+          <t>读不到这个文件，请重试。</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -7806,17 +7806,17 @@
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>On Write Finished</t>
         </is>
       </c>
       <c r="D283" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E283" s="7" t="inlineStr">
         <is>
-          <t>应用备份</t>
+          <t>导出失败，请换一个位置重试</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="C284" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Restore Confirm Dialog</t>
         </is>
       </c>
       <c r="D284" s="7" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>把记账、账本、账户、余额、类别和设置「全部」存成一个文件。备份不可选范围，恢复时用这个文件覆盖当前全部数据。</t>
+          <t>备份时间：{DateLabels.dayLabel(exportDateKey(file.createdAt))}　备份版本：{file.appVersion.ifBlank { "未知" }}</t>
         </is>
       </c>
       <c r="F284" s="5" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Restore Confirm Dialog</t>
         </is>
       </c>
       <c r="D285" s="7" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="E285" s="7" t="inlineStr">
         <is>
-          <t>正在恢复，请不要退出…</t>
+          <t>将使用此备份覆盖当前全部数据：{file.tables.size} 张表、{file.rowCount} 条记录。</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="C286" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Restore Confirm Dialog</t>
         </is>
       </c>
       <c r="D286" s="7" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>这个选择下还没有记录可导出。</t>
+          <t>当前的数据会被替换掉，且无法撤销。建议先导出一份现在的备份。</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Export Screen</t>
+          <t>Restore Confirm Dialog</t>
         </is>
       </c>
       <c r="D287" s="7" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="E287" s="7" t="inlineStr">
         <is>
-          <t>选择之前导出的备份，用它覆盖当前的全部数据</t>
+          <t>恢复备份</t>
         </is>
       </c>
       <c r="F287" s="5" t="n"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C288" s="7" t="inlineStr">
         <is>
-          <t>Export Screen；On Backup Write Finished</t>
+          <t>Restore Confirm Dialog</t>
         </is>
       </c>
       <c r="D288" s="7" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>备份已导出</t>
+          <t>覆盖并恢复</t>
         </is>
       </c>
       <c r="F288" s="5" t="n"/>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="C289" s="7" t="inlineStr">
         <is>
-          <t>Export Screen；On Write Finished</t>
+          <t>Stage Restore</t>
         </is>
       </c>
       <c r="D289" s="7" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="E289" s="7" t="inlineStr">
         <is>
-          <t>已导出</t>
+          <t>备份文件不可读。</t>
         </is>
       </c>
       <c r="F289" s="5" t="n"/>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="C290" s="7" t="inlineStr">
         <is>
-          <t>Export Screen；设置 · Settings Screen</t>
+          <t>Target Picker Dialog</t>
         </is>
       </c>
       <c r="D290" s="7" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>选择需要导出的账本</t>
         </is>
       </c>
       <c r="F290" s="5" t="n"/>
@@ -8014,17 +8014,17 @@
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>On Backup Write Finished</t>
+          <t>Target Picker Dialog；Target Label</t>
         </is>
       </c>
       <c r="D291" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr">
         <is>
-          <t>备份导出失败，请换一个位置重试</t>
+          <t>全部账本</t>
         </is>
       </c>
       <c r="F291" s="5" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="C292" s="7" t="inlineStr">
         <is>
-          <t>On Restore Read Failed</t>
+          <t>Txn Row</t>
         </is>
       </c>
       <c r="D292" s="7" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>读不到这个文件，请换一个再试。</t>
+          <t>否</t>
         </is>
       </c>
       <c r="F292" s="5" t="n"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="C293" s="7" t="inlineStr">
         <is>
-          <t>On Write Finished</t>
+          <t>Txn Row</t>
         </is>
       </c>
       <c r="D293" s="7" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="E293" s="7" t="inlineStr">
         <is>
-          <t>导出失败，请换一个位置重试</t>
+          <t>是</t>
         </is>
       </c>
       <c r="F293" s="5" t="n"/>
@@ -8092,17 +8092,17 @@
       </c>
       <c r="C294" s="7" t="inlineStr">
         <is>
-          <t>Restore Confirm Dialog</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="D294" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E294" s="7" t="inlineStr">
         <is>
-          <t>备份时间：{DateLabels.dayLabel(exportDateKey(file.createdAt))}　备份版本：{file.appVersion.ifBlank { "未知" }}</t>
+          <t>全部记录</t>
         </is>
       </c>
       <c r="F294" s="5" t="n"/>
@@ -8118,17 +8118,17 @@
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Restore Confirm Dialog</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="D295" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E295" s="7" t="inlineStr">
         <is>
-          <t>将用这个备份覆盖当前全部数据：{file.tables.size} 张表、{file.rowCount} 条记录。</t>
+          <t>只导出本月</t>
         </is>
       </c>
       <c r="F295" s="5" t="n"/>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="C296" s="7" t="inlineStr">
         <is>
-          <t>Restore Confirm Dialog</t>
+          <t>导出与备份</t>
         </is>
       </c>
       <c r="D296" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
         <is>
-          <t>当前的数据会被替换掉，且无法撤销。建议先导出一份现在的备份。</t>
+          <t>所选账本的所有流水</t>
         </is>
       </c>
       <c r="F296" s="5" t="n"/>
@@ -8170,43 +8170,43 @@
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Restore Confirm Dialog</t>
+          <t>导出与备份；统计</t>
         </is>
       </c>
       <c r="D297" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>选项名称</t>
         </is>
       </c>
       <c r="E297" s="7" t="inlineStr">
         <is>
-          <t>恢复备份</t>
+          <t>本月</t>
         </is>
       </c>
       <c r="F297" s="5" t="n"/>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="n">
+      <c r="A298" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="B298" s="7" t="inlineStr">
-        <is>
-          <t>导出与备份</t>
-        </is>
-      </c>
-      <c r="C298" s="7" t="inlineStr">
-        <is>
-          <t>Restore Confirm Dialog</t>
-        </is>
-      </c>
-      <c r="D298" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E298" s="7" t="inlineStr">
-        <is>
-          <t>覆盖并恢复</t>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>About Screen</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>数据存放与使用条款</t>
         </is>
       </c>
       <c r="F298" s="5" t="n"/>
@@ -8217,12 +8217,12 @@
       </c>
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>Stage Restore</t>
+          <t>About Screen</t>
         </is>
       </c>
       <c r="D299" s="7" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="E299" s="7" t="inlineStr">
         <is>
-          <t>备份文件读不了。</t>
+          <t>版本 {versionName}</t>
         </is>
       </c>
       <c r="F299" s="5" t="n"/>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="B300" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C300" s="7" t="inlineStr">
         <is>
-          <t>Target Picker Dialog</t>
+          <t>About Screen</t>
         </is>
       </c>
       <c r="D300" s="7" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>导出哪个账本</t>
+          <t>逐项说明记账本的各项功能</t>
         </is>
       </c>
       <c r="F300" s="5" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>Target Picker Dialog</t>
+          <t>About Screen；Feature Guide Screen</t>
         </is>
       </c>
       <c r="D301" s="7" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="E301" s="7" t="inlineStr">
         <is>
-          <t>每个账本各占一列「账本」区分</t>
+          <t>功能介绍</t>
         </is>
       </c>
       <c r="F301" s="5" t="n"/>
@@ -8295,22 +8295,22 @@
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C302" s="7" t="inlineStr">
         <is>
-          <t>Target Picker Dialog；Target Label</t>
+          <t>About Screen；Settings Screen</t>
         </is>
       </c>
       <c r="D302" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E302" s="7" t="inlineStr">
         <is>
-          <t>全部账本</t>
+          <t>关于</t>
         </is>
       </c>
       <c r="F302" s="5" t="n"/>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="B303" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>Txn Row</t>
+          <t>About Screen；Terms Of Use Screen</t>
         </is>
       </c>
       <c r="D303" s="7" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E303" s="7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>用户协议</t>
         </is>
       </c>
       <c r="F303" s="5" t="n"/>
@@ -8347,12 +8347,12 @@
       </c>
       <c r="B304" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C304" s="7" t="inlineStr">
         <is>
-          <t>Txn Row</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D304" s="7" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="E304" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>修改与删除</t>
         </is>
       </c>
       <c r="F304" s="5" t="n"/>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="B305" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D305" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E305" s="7" t="inlineStr">
         <is>
-          <t>全部记录</t>
+          <t>具备账户与余额概念，可设置每月生活费与各类别预算，适用于日常收支管理。</t>
         </is>
       </c>
       <c r="F305" s="5" t="n"/>
@@ -8399,22 +8399,22 @@
       </c>
       <c r="B306" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C306" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D306" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E306" s="7" t="inlineStr">
         <is>
-          <t>只导出本月</t>
+          <t>只记录收入与支出，不区分账户，适用于记录单项累计账目。</t>
         </is>
       </c>
       <c r="F306" s="5" t="n"/>
@@ -8425,22 +8425,22 @@
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D307" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E307" s="7" t="inlineStr">
         <is>
-          <t>所选账本的所有流水</t>
+          <t>在「明细」页点击任意一条记录进入详情页，可查看完整信息或进入编辑页修改，修改后详情页与各统计页面立即更新。</t>
         </is>
       </c>
       <c r="F307" s="5" t="n"/>
@@ -8451,48 +8451,48 @@
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>导出与备份</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="C308" s="7" t="inlineStr">
         <is>
-          <t>导出与备份；统计</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D308" s="7" t="inlineStr">
         <is>
-          <t>选项名称</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E308" s="7" t="inlineStr">
         <is>
-          <t>本月</t>
+          <t>在「明细」页点击右下角按钮进入记账页，通过数字键盘输入金额，并选择收支方向、类别与账户。日期默认为当天，可在顶部修改。</t>
         </is>
       </c>
       <c r="F308" s="5" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="n">
+      <c r="A309" s="6" t="n">
         <v>306</v>
       </c>
-      <c r="B309" s="4" t="inlineStr">
+      <c r="B309" s="7" t="inlineStr">
         <is>
           <t>设置</t>
         </is>
       </c>
-      <c r="C309" s="4" t="inlineStr">
-        <is>
-          <t>About Screen</t>
-        </is>
-      </c>
-      <c r="D309" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E309" s="4" t="inlineStr">
-        <is>
-          <t>数据存放与使用条款</t>
+      <c r="C309" s="7" t="inlineStr">
+        <is>
+          <t>FEATURES</t>
+        </is>
+      </c>
+      <c r="D309" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E309" s="7" t="inlineStr">
+        <is>
+          <t>在主屏幕添加小组件，直接查看当月的支出或剩余额度。</t>
         </is>
       </c>
       <c r="F309" s="5" t="n"/>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C310" s="7" t="inlineStr">
         <is>
-          <t>About Screen</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D310" s="7" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="E310" s="7" t="inlineStr">
         <is>
-          <t>版本 {versionName}</t>
+          <t>增删改各类别，并调整其归属的大类。类别用于记账时的归类和统计时的汇总。</t>
         </is>
       </c>
       <c r="F310" s="5" t="n"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C311" s="7" t="inlineStr">
         <is>
-          <t>About Screen</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D311" s="7" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="E311" s="7" t="inlineStr">
         <is>
-          <t>逐项说明记账本的各项功能</t>
+          <t>导入微信、支付宝导出的账单文件（CSV 或 xlsx），或本应用导出的 CSV 文件。导入前会逐条列出待确认的记录，可选择目标账本、修改收支方向与类别；重复记录会自动识别并跳过，导入后可整批撤销。</t>
         </is>
       </c>
       <c r="F311" s="5" t="n"/>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="C312" s="7" t="inlineStr">
         <is>
-          <t>About Screen；Feature Guide Screen</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D312" s="7" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E312" s="7" t="inlineStr">
         <is>
-          <t>功能介绍</t>
+          <t>导出数据</t>
         </is>
       </c>
       <c r="F312" s="5" t="n"/>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>About Screen；Settings Screen</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D313" s="7" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="E313" s="7" t="inlineStr">
         <is>
-          <t>关于</t>
+          <t>将不再使用的账本收起。归档后的账本仍可查看，但不能修改其中的记账条目。</t>
         </is>
       </c>
       <c r="F313" s="5" t="n"/>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="C314" s="7" t="inlineStr">
         <is>
-          <t>About Screen；Terms Of Use Screen</t>
+          <t>FEATURES</t>
         </is>
       </c>
       <c r="D314" s="7" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="E314" s="7" t="inlineStr">
         <is>
-          <t>用户协议</t>
+          <t>将当前账本的全部记账条目导出为 CSV 文件，用于备份或在其他软件中查看。</t>
         </is>
       </c>
       <c r="F314" s="5" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E315" s="7" t="inlineStr">
         <is>
-          <t>修改与删除</t>
+          <t>当本月支出接近或超出所设预算时，通过通知提醒。</t>
         </is>
       </c>
       <c r="F315" s="5" t="n"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>具备账户与余额概念，可设置每月生活费与各类别预算，适用于日常收支管理。</t>
+          <t>指定记账页直接显示的类别，其余类别收进「更多」菜单。未指定时按最近使用情况自动排列。</t>
         </is>
       </c>
       <c r="F316" s="5" t="n"/>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E317" s="7" t="inlineStr">
         <is>
-          <t>只记录收入与支出，不区分账户，适用于记录单项累计账目。</t>
+          <t>按关键词、日期区间、类别、账户、收支方向与金额区间筛选记账条目。</t>
         </is>
       </c>
       <c r="F317" s="5" t="n"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="E318" s="7" t="inlineStr">
         <is>
-          <t>在「明细」页点击任意一条记录进入详情页，可查看完整信息或进入编辑页修改，修改后详情页与各统计页面立即更新。</t>
+          <t>按日列出当月全部记账条目，并显示每日支出与收入合计。可切换日历视图，日历上按日显示收支金额，点击某日可只看当天的记录。</t>
         </is>
       </c>
       <c r="F318" s="5" t="n"/>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="E319" s="7" t="inlineStr">
         <is>
-          <t>在「明细」页点击右下角按钮进入记账页，通过数字键盘输入金额，并选择收支方向、类别与账户。日期默认为当天，可在顶部修改。</t>
+          <t>按本月、近三十天、今年、学期或全部时间范围，以图表展示支出构成与收支趋势。</t>
         </is>
       </c>
       <c r="F319" s="5" t="n"/>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E320" s="7" t="inlineStr">
         <is>
-          <t>在主屏幕添加小组件，直接查看当月的支出或剩余额度。</t>
+          <t>支持建立多个账本，分别记录不同的账目。可对账本进行新建、改名、归档与删除操作。</t>
         </is>
       </c>
       <c r="F320" s="5" t="n"/>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="E321" s="7" t="inlineStr">
         <is>
-          <t>增删改各类别，并调整其归属的大类。类别用于记账时的归类和统计时的汇总。</t>
+          <t>查看与统计</t>
         </is>
       </c>
       <c r="F321" s="5" t="n"/>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="E322" s="7" t="inlineStr">
         <is>
-          <t>导入微信、支付宝导出的账单文件（CSV 或 xlsx），或本应用导出的 CSV 文件。导入前会逐条列出待确认的记录，可选择目标账本、修改收支方向与类别；重复记录会自动识别并跳过，导入后可整批撤销。</t>
+          <t>桌面小组件</t>
         </is>
       </c>
       <c r="F322" s="5" t="n"/>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="E323" s="7" t="inlineStr">
         <is>
-          <t>导出数据</t>
+          <t>管理现金、银行卡、支付宝、微信等账户，并查看各账户余额。余额可通过设置余额锚点进行校准。</t>
         </is>
       </c>
       <c r="F323" s="5" t="n"/>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="E324" s="7" t="inlineStr">
         <is>
-          <t>将不再使用的账本收起。归档后的账本仍可查看，但不能修改其中的记账条目。</t>
+          <t>类别与账户</t>
         </is>
       </c>
       <c r="F324" s="5" t="n"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="E325" s="7" t="inlineStr">
         <is>
-          <t>将当前账本的全部记账条目导出为 CSV 文件，用于备份或在其他软件中查看。</t>
+          <t>记录分期或按月扣款的支出计划，例如数码产品分期、房租月付。计划到期后自动生成对应的记账条目。</t>
         </is>
       </c>
       <c r="F325" s="5" t="n"/>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="E326" s="7" t="inlineStr">
         <is>
-          <t>当本月支出接近或超出所设预算时，通过通知提醒。</t>
+          <t>记录账户之间的资金划转。转入转出金额相同，手续费单独计为支出，不计入收入或支出总额。</t>
         </is>
       </c>
       <c r="F326" s="5" t="n"/>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="E327" s="7" t="inlineStr">
         <is>
-          <t>指定记账页直接显示的类别，其余类别收进「更多」菜单。未指定时按最近使用情况自动排列。</t>
+          <t>记账录入</t>
         </is>
       </c>
       <c r="F327" s="5" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="E328" s="7" t="inlineStr">
         <is>
-          <t>按关键词、日期区间、类别、账户、收支方向与金额区间筛选记账条目。</t>
+          <t>设置统计页「学期」模式所使用的日期区间，适用于按学期查看开支。</t>
         </is>
       </c>
       <c r="F328" s="5" t="n"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D329" s="7" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="E329" s="7" t="inlineStr">
         <is>
-          <t>按日列出当月全部记账条目，并显示每日支出与收入合计。可切换日历视图，日历上按日显示收支金额，点击某日可只看当天的记录。</t>
+          <t>归档</t>
         </is>
       </c>
       <c r="F329" s="5" t="n"/>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；Ledger Settings Screen；Settings Screen</t>
         </is>
       </c>
       <c r="D330" s="7" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="E330" s="7" t="inlineStr">
         <is>
-          <t>按本月、近三十天、今年、学期或全部时间范围，以图表展示支出构成与收支趋势。</t>
+          <t>账本管理</t>
         </is>
       </c>
       <c r="F330" s="5" t="n"/>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；Pinned Categories Screen；Settings Screen</t>
         </is>
       </c>
       <c r="D331" s="7" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="E331" s="7" t="inlineStr">
         <is>
-          <t>支持建立多个账本，分别记录不同的账目。可对账本进行新建、改名、归档与删除操作。</t>
+          <t>类目快捷选择</t>
         </is>
       </c>
       <c r="F331" s="5" t="n"/>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；Settings Screen</t>
         </is>
       </c>
       <c r="D332" s="7" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="E332" s="7" t="inlineStr">
         <is>
-          <t>查看与统计</t>
+          <t>数据</t>
         </is>
       </c>
       <c r="F332" s="5" t="n"/>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；Settings Screen</t>
         </is>
       </c>
       <c r="D333" s="7" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="E333" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>记账</t>
         </is>
       </c>
       <c r="F333" s="5" t="n"/>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="C334" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；Settings Screen；Term Settings Screen</t>
         </is>
       </c>
       <c r="D334" s="7" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t>管理现金、银行卡、支付宝、微信等账户，并查看各账户余额。余额可通过设置余额锚点进行校准。</t>
+          <t>学期设置</t>
         </is>
       </c>
       <c r="F334" s="5" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；底部导航 · Budget</t>
         </is>
       </c>
       <c r="D335" s="7" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t>类别与账户</t>
+          <t>明细</t>
         </is>
       </c>
       <c r="F335" s="5" t="n"/>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；系统通知 · Ensure Channel</t>
         </is>
       </c>
       <c r="D336" s="7" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="E336" s="7" t="inlineStr">
         <is>
-          <t>记录分期或按月扣款的支出计划，例如数码产品分期、房租月付。计划到期后自动生成对应的记账条目。</t>
+          <t>预算提醒</t>
         </is>
       </c>
       <c r="F336" s="5" t="n"/>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>FEATURES；统计 · Stats Screen；底部导航 · Budget</t>
         </is>
       </c>
       <c r="D337" s="7" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="E337" s="7" t="inlineStr">
         <is>
-          <t>记录账户之间的资金划转。转入转出金额相同，手续费单独计为支出，不计入收入或支出总额。</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="F337" s="5" t="n"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="C338" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>Ledger Card</t>
         </is>
       </c>
       <c r="D338" s="7" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E338" s="7" t="inlineStr">
         <is>
-          <t>记账录入</t>
+          <t xml:space="preserve"> · 已归档</t>
         </is>
       </c>
       <c r="F338" s="5" t="n"/>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>FEATURES</t>
+          <t>Ledger Card</t>
         </is>
       </c>
       <c r="D339" s="7" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="E339" s="7" t="inlineStr">
         <is>
-          <t>设置统计页「学期」模式所使用的日期区间，适用于按学期查看开支。</t>
+          <t xml:space="preserve"> · 当前</t>
         </is>
       </c>
       <c r="F339" s="5" t="n"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；Ledger Editor Dialog</t>
+          <t>Ledger Card</t>
         </is>
       </c>
       <c r="D340" s="7" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="E340" s="7" t="inlineStr">
         <is>
-          <t>归档</t>
+          <t>编辑</t>
         </is>
       </c>
       <c r="F340" s="5" t="n"/>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；Ledger Settings Screen；Settings Screen</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D341" s="7" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="E341" s="7" t="inlineStr">
         <is>
-          <t>账本管理</t>
+          <t>「{existing.name}」和它下面的所有记账条目都会被删除。</t>
         </is>
       </c>
       <c r="F341" s="5" t="n"/>
@@ -9340,17 +9340,17 @@
       </c>
       <c r="C342" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；Pinned Categories Screen；Settings Screen</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D342" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E342" s="7" t="inlineStr">
         <is>
-          <t>类目快捷选择</t>
+          <t>删除账本</t>
         </is>
       </c>
       <c r="F342" s="5" t="n"/>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；Settings Screen</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D343" s="7" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E343" s="7" t="inlineStr">
         <is>
-          <t>数据</t>
+          <t>取消归档</t>
         </is>
       </c>
       <c r="F343" s="5" t="n"/>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="C344" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；Settings Screen</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D344" s="7" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="E344" s="7" t="inlineStr">
         <is>
-          <t>记账</t>
+          <t>新建账本</t>
         </is>
       </c>
       <c r="F344" s="5" t="n"/>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；Settings Screen；Term Settings Screen</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D345" s="7" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="E345" s="7" t="inlineStr">
         <is>
-          <t>学期设置</t>
+          <t>编辑账本</t>
         </is>
       </c>
       <c r="F345" s="5" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；底部导航 · Budget</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D346" s="7" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="E346" s="7" t="inlineStr">
         <is>
-          <t>明细</t>
+          <t>至少要保留一个账本。</t>
         </is>
       </c>
       <c r="F346" s="5" t="n"/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；系统通知 · Ensure Channel</t>
+          <t>Ledger Editor Dialog</t>
         </is>
       </c>
       <c r="D347" s="7" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="E347" s="7" t="inlineStr">
         <is>
-          <t>预算提醒</t>
+          <t>账本创建后不能再改记账方式，否则已有数据会失去归属。</t>
         </is>
       </c>
       <c r="F347" s="5" t="n"/>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="C348" s="7" t="inlineStr">
         <is>
-          <t>FEATURES；统计 · Stats Screen；底部导航 · Budget</t>
+          <t>Ledger Settings Screen</t>
         </is>
       </c>
       <c r="D348" s="7" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E348" s="7" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>在这里新建、删除、更改账本设置</t>
         </is>
       </c>
       <c r="F348" s="5" t="n"/>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Ledger Card</t>
+          <t>Pinned Categories Screen</t>
         </is>
       </c>
       <c r="D349" s="7" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="E349" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · 已归档</t>
+          <t>已自定义：{state.pinnedCount} 个类别直接显示，其余收在「更多」里。</t>
         </is>
       </c>
       <c r="F349" s="5" t="n"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C350" s="7" t="inlineStr">
         <is>
-          <t>Ledger Card</t>
+          <t>Pinned Categories Screen</t>
         </is>
       </c>
       <c r="D350" s="7" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="E350" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> · 当前</t>
+          <t>当前显示前 {state.defaultCount} 个类别，其余收在「更多」里。改动任意一项即转为自定义。</t>
         </is>
       </c>
       <c r="F350" s="5" t="n"/>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Ledger Card</t>
+          <t>Pinned Categories Screen</t>
         </is>
       </c>
       <c r="D351" s="7" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="E351" s="7" t="inlineStr">
         <is>
-          <t>编辑</t>
+          <t>恢复默认</t>
         </is>
       </c>
       <c r="F351" s="5" t="n"/>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Pinned Categories Screen</t>
         </is>
       </c>
       <c r="D352" s="7" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="E352" s="7" t="inlineStr">
         <is>
-          <t>「{existing.name}」和它下面的所有记账条目都会被删除。</t>
+          <t>选择在记账时可快捷选择的类目</t>
         </is>
       </c>
       <c r="F352" s="5" t="n"/>
@@ -9626,17 +9626,17 @@
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Settings Screen</t>
         </is>
       </c>
       <c r="D353" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E353" s="7" t="inlineStr">
         <is>
-          <t>删除账本</t>
+          <t>关于记账本</t>
         </is>
       </c>
       <c r="F353" s="5" t="n"/>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="C354" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Settings Screen；底部导航 · Budget</t>
         </is>
       </c>
       <c r="D354" s="7" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="E354" s="7" t="inlineStr">
         <is>
-          <t>取消归档</t>
+          <t>设置</t>
         </is>
       </c>
       <c r="F354" s="5" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Suggested Term Name</t>
         </is>
       </c>
       <c r="D355" s="7" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="E355" s="7" t="inlineStr">
         <is>
-          <t>新建账本</t>
+          <t>春季学期</t>
         </is>
       </c>
       <c r="F355" s="5" t="n"/>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="C356" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Suggested Term Name</t>
         </is>
       </c>
       <c r="D356" s="7" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="E356" s="7" t="inlineStr">
         <is>
-          <t>编辑账本</t>
+          <t>秋季学期</t>
         </is>
       </c>
       <c r="F356" s="5" t="n"/>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Term Card</t>
         </is>
       </c>
       <c r="D357" s="7" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="E357" s="7" t="inlineStr">
         <is>
-          <t>至少要保留一个账本。</t>
+          <t>{DateKeys.parseDateKey(row.term.startDateKey)} 起 · 共 {row.dayCount} 天</t>
         </is>
       </c>
       <c r="F357" s="5" t="n"/>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>Ledger Editor Dialog</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D358" s="7" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E358" s="7" t="inlineStr">
         <is>
-          <t>账本创建后不能再改记账方式，否则已有数据会失去归属。</t>
+          <t>「{existing.name}」这个日期区间会被移除。</t>
         </is>
       </c>
       <c r="F358" s="5" t="n"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Ledger Settings Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D359" s="7" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="E359" s="7" t="inlineStr">
         <is>
-          <t>在这里新建、删除、更改账本设置</t>
+          <t>一学期后</t>
         </is>
       </c>
       <c r="F359" s="5" t="n"/>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="C360" s="7" t="inlineStr">
         <is>
-          <t>Pinned Categories Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D360" s="7" t="inlineStr">
@@ -9818,8 +9818,7 @@
       </c>
       <c r="E360" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-收入类别数量少，始终全部显示，不参与这里的收纳。</t>
+          <t>今天开始</t>
         </is>
       </c>
       <c r="F360" s="5" t="n"/>
@@ -9835,17 +9834,17 @@
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Pinned Categories Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D361" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E361" s="7" t="inlineStr">
         <is>
-          <t>已自定义：{state.pinnedCount} 个类别直接显示，其余收在「更多」里。</t>
+          <t>删除学期</t>
         </is>
       </c>
       <c r="F361" s="5" t="n"/>
@@ -9861,17 +9860,17 @@
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>Pinned Categories Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D362" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E362" s="7" t="inlineStr">
         <is>
-          <t>当前显示前 {state.defaultCount} 个类别，其余收在「更多」里。改动任意一项即转为自定义。</t>
+          <t>删除这个学期</t>
         </is>
       </c>
       <c r="F362" s="5" t="n"/>
@@ -9887,17 +9886,17 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Pinned Categories Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D363" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E363" s="7" t="inlineStr">
         <is>
-          <t>恢复默认</t>
+          <t>开始日期</t>
         </is>
       </c>
       <c r="F363" s="5" t="n"/>
@@ -9913,7 +9912,7 @@
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>Pinned Categories Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D364" s="7" t="inlineStr">
@@ -9923,7 +9922,7 @@
       </c>
       <c r="E364" s="7" t="inlineStr">
         <is>
-          <t>选择在记账时可快捷选择的类目</t>
+          <t>添加学期</t>
         </is>
       </c>
       <c r="F364" s="5" t="n"/>
@@ -9939,17 +9938,17 @@
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Settings Screen</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D365" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标签 / 选项卡</t>
         </is>
       </c>
       <c r="E365" s="7" t="inlineStr">
         <is>
-          <t>关于记账本</t>
+          <t>结束日期</t>
         </is>
       </c>
       <c r="F365" s="5" t="n"/>
@@ -9965,7 +9964,7 @@
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>Settings Screen；底部导航 · Budget</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D366" s="7" t="inlineStr">
@@ -9975,7 +9974,7 @@
       </c>
       <c r="E366" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>结束日期不能早于开始日期</t>
         </is>
       </c>
       <c r="F366" s="5" t="n"/>
@@ -9991,7 +9990,7 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Suggested Term Name</t>
+          <t>Term Editor Dialog</t>
         </is>
       </c>
       <c r="D367" s="7" t="inlineStr">
@@ -10001,7 +10000,7 @@
       </c>
       <c r="E367" s="7" t="inlineStr">
         <is>
-          <t>春季学期</t>
+          <t>编辑学期</t>
         </is>
       </c>
       <c r="F367" s="5" t="n"/>
@@ -10017,7 +10016,7 @@
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>Suggested Term Name</t>
+          <t>Term Settings Screen</t>
         </is>
       </c>
       <c r="D368" s="7" t="inlineStr">
@@ -10027,7 +10026,7 @@
       </c>
       <c r="E368" s="7" t="inlineStr">
         <is>
-          <t>秋季学期</t>
+          <t>【{state.ledgerName}】还没有学期，点右上角「添加」建一个。学期是按账本分开的。</t>
         </is>
       </c>
       <c r="F368" s="5" t="n"/>
@@ -10043,7 +10042,7 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Term Card</t>
+          <t>Term Settings Screen</t>
         </is>
       </c>
       <c r="D369" s="7" t="inlineStr">
@@ -10053,7 +10052,7 @@
       </c>
       <c r="E369" s="7" t="inlineStr">
         <is>
-          <t>{DateKeys.parseDateKey(row.term.startDateKey)} 起 · 共 {row.dayCount} 天</t>
+          <t>设置【统计】页中学期模式中的日期范围</t>
         </is>
       </c>
       <c r="F369" s="5" t="n"/>
@@ -10069,7 +10068,7 @@
       </c>
       <c r="C370" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Term Settings Screen</t>
         </is>
       </c>
       <c r="D370" s="7" t="inlineStr">
@@ -10079,7 +10078,7 @@
       </c>
       <c r="E370" s="7" t="inlineStr">
         <is>
-          <t>「{existing.name}」这个日期区间会被移除。</t>
+          <t>还没有学期，点右上角「添加」建一个</t>
         </is>
       </c>
       <c r="F370" s="5" t="n"/>
@@ -10095,7 +10094,7 @@
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Terms Of Use Screen</t>
         </is>
       </c>
       <c r="D371" s="7" t="inlineStr">
@@ -10105,7 +10104,7 @@
       </c>
       <c r="E371" s="7" t="inlineStr">
         <is>
-          <t>一学期后</t>
+          <t>其余条款待补充。</t>
         </is>
       </c>
       <c r="F371" s="5" t="n"/>
@@ -10121,17 +10120,17 @@
       </c>
       <c r="C372" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Terms Of Use Screen</t>
         </is>
       </c>
       <c r="D372" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="E372" s="7" t="inlineStr">
         <is>
-          <t>今天开始</t>
+          <t>数据存放</t>
         </is>
       </c>
       <c r="F372" s="5" t="n"/>
@@ -10147,43 +10146,43 @@
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Terms Of Use Screen</t>
         </is>
       </c>
       <c r="D373" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E373" s="7" t="inlineStr">
         <is>
-          <t>删除学期</t>
+          <t>本应用全部数据均保存于本地，不上传网络，请及时备份好数据以免丢失。</t>
         </is>
       </c>
       <c r="F373" s="5" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="6" t="n">
+      <c r="A374" s="3" t="n">
         <v>371</v>
       </c>
-      <c r="B374" s="7" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="C374" s="7" t="inlineStr">
-        <is>
-          <t>Term Editor Dialog</t>
-        </is>
-      </c>
-      <c r="D374" s="7" t="inlineStr">
-        <is>
-          <t>标签 / 选项卡</t>
-        </is>
-      </c>
-      <c r="E374" s="7" t="inlineStr">
-        <is>
-          <t>删除这个学期</t>
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>通用界面组件</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr">
+        <is>
+          <t>Calendar Picker Dialog</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>回到今天</t>
         </is>
       </c>
       <c r="F374" s="5" t="n"/>
@@ -10194,22 +10193,22 @@
       </c>
       <c r="B375" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Calendar Picker Dialog</t>
         </is>
       </c>
       <c r="D375" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E375" s="7" t="inlineStr">
         <is>
-          <t>开始日期</t>
+          <t>选择日期</t>
         </is>
       </c>
       <c r="F375" s="5" t="n"/>
@@ -10220,12 +10219,12 @@
       </c>
       <c r="B376" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Confirm Delete Dialog</t>
         </is>
       </c>
       <c r="D376" s="7" t="inlineStr">
@@ -10235,7 +10234,7 @@
       </c>
       <c r="E376" s="7" t="inlineStr">
         <is>
-          <t>添加学期</t>
+          <t>删除后无法恢复，请谨慎操作。</t>
         </is>
       </c>
       <c r="F376" s="5" t="n"/>
@@ -10246,22 +10245,22 @@
       </c>
       <c r="B377" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Ledger Switcher Dialog</t>
         </is>
       </c>
       <c r="D377" s="7" t="inlineStr">
         <is>
-          <t>标签 / 选项卡</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E377" s="7" t="inlineStr">
         <is>
-          <t>结束日期</t>
+          <t>关闭</t>
         </is>
       </c>
       <c r="F377" s="5" t="n"/>
@@ -10272,12 +10271,12 @@
       </c>
       <c r="B378" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C378" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Ledger Switcher Dialog</t>
         </is>
       </c>
       <c r="D378" s="7" t="inlineStr">
@@ -10287,7 +10286,7 @@
       </c>
       <c r="E378" s="7" t="inlineStr">
         <is>
-          <t>结束日期不能早于开始日期</t>
+          <t>切换账本</t>
         </is>
       </c>
       <c r="F378" s="5" t="n"/>
@@ -10298,12 +10297,12 @@
       </c>
       <c r="B379" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Term Editor Dialog</t>
+          <t>Ledger Switcher Dialog</t>
         </is>
       </c>
       <c r="D379" s="7" t="inlineStr">
@@ -10313,7 +10312,7 @@
       </c>
       <c r="E379" s="7" t="inlineStr">
         <is>
-          <t>编辑学期</t>
+          <t>当前</t>
         </is>
       </c>
       <c r="F379" s="5" t="n"/>
@@ -10324,12 +10323,12 @@
       </c>
       <c r="B380" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C380" s="7" t="inlineStr">
         <is>
-          <t>Term Settings Screen</t>
+          <t>Ledger Switcher Dialog</t>
         </is>
       </c>
       <c r="D380" s="7" t="inlineStr">
@@ -10339,7 +10338,7 @@
       </c>
       <c r="E380" s="7" t="inlineStr">
         <is>
-          <t>【{state.ledgerName}】还没有学期，点右上角「添加」建一个。学期是按账本分开的。</t>
+          <t>还没有账本。去「设置 → 账本管理」新建一个。</t>
         </is>
       </c>
       <c r="F380" s="5" t="n"/>
@@ -10350,12 +10349,12 @@
       </c>
       <c r="B381" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>Term Settings Screen</t>
+          <t>Month Pager</t>
         </is>
       </c>
       <c r="D381" s="7" t="inlineStr">
@@ -10365,7 +10364,7 @@
       </c>
       <c r="E381" s="7" t="inlineStr">
         <is>
-          <t>设置【统计】页中学期模式中的日期范围</t>
+          <t>%d 年 %d 月</t>
         </is>
       </c>
       <c r="F381" s="5" t="n"/>
@@ -10376,12 +10375,12 @@
       </c>
       <c r="B382" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C382" s="7" t="inlineStr">
         <is>
-          <t>Term Settings Screen</t>
+          <t>Wheel</t>
         </is>
       </c>
       <c r="D382" s="7" t="inlineStr">
@@ -10391,7 +10390,7 @@
       </c>
       <c r="E382" s="7" t="inlineStr">
         <is>
-          <t>还没有学期，点右上角「添加」建一个</t>
+          <t>%02d</t>
         </is>
       </c>
       <c r="F382" s="5" t="n"/>
@@ -10402,12 +10401,12 @@
       </c>
       <c r="B383" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Terms Of Use Screen</t>
+          <t>Wheel Time Picker Dialog</t>
         </is>
       </c>
       <c r="D383" s="7" t="inlineStr">
@@ -10417,7 +10416,7 @@
       </c>
       <c r="E383" s="7" t="inlineStr">
         <is>
-          <t>全部数据保存在本机数据库里，不联网、不上传、没有账号。卸载 App 会一并删除，重要数据请自行导出备份。</t>
+          <t>:</t>
         </is>
       </c>
       <c r="F383" s="5" t="n"/>
@@ -10428,12 +10427,12 @@
       </c>
       <c r="B384" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C384" s="7" t="inlineStr">
         <is>
-          <t>Terms Of Use Screen</t>
+          <t>Wheel Time Picker Dialog</t>
         </is>
       </c>
       <c r="D384" s="7" t="inlineStr">
@@ -10443,7 +10442,7 @@
       </c>
       <c r="E384" s="7" t="inlineStr">
         <is>
-          <t>其余条款待补充。</t>
+          <t>当前 %02d:%02d</t>
         </is>
       </c>
       <c r="F384" s="5" t="n"/>
@@ -10454,22 +10453,22 @@
       </c>
       <c r="B385" s="7" t="inlineStr">
         <is>
-          <t>设置</t>
+          <t>通用界面组件</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Terms Of Use Screen</t>
+          <t>Wheel Time Picker Dialog</t>
         </is>
       </c>
       <c r="D385" s="7" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E385" s="7" t="inlineStr">
         <is>
-          <t>数据存放</t>
+          <t>选择时间</t>
         </is>
       </c>
       <c r="F385" s="5" t="n"/>
@@ -10480,12 +10479,12 @@
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Calendar Picker Dialog</t>
+          <t>Day Label With Relative</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -10495,7 +10494,7 @@
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
-          <t>回到今天</t>
+          <t xml:space="preserve">今天 · </t>
         </is>
       </c>
       <c r="F386" s="5" t="n"/>
@@ -10506,12 +10505,12 @@
       </c>
       <c r="B387" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>Calendar Picker Dialog</t>
+          <t>Day Label With Relative</t>
         </is>
       </c>
       <c r="D387" s="7" t="inlineStr">
@@ -10521,7 +10520,7 @@
       </c>
       <c r="E387" s="7" t="inlineStr">
         <is>
-          <t>选择日期</t>
+          <t xml:space="preserve">明天 · </t>
         </is>
       </c>
       <c r="F387" s="5" t="n"/>
@@ -10532,12 +10531,12 @@
       </c>
       <c r="B388" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C388" s="7" t="inlineStr">
         <is>
-          <t>Confirm Delete Dialog</t>
+          <t>Day Label With Relative</t>
         </is>
       </c>
       <c r="D388" s="7" t="inlineStr">
@@ -10547,7 +10546,7 @@
       </c>
       <c r="E388" s="7" t="inlineStr">
         <is>
-          <t>删除后无法恢复，请谨慎操作。</t>
+          <t xml:space="preserve">昨天 · </t>
         </is>
       </c>
       <c r="F388" s="5" t="n"/>
@@ -10558,12 +10557,12 @@
       </c>
       <c r="B389" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Ledger Switcher Dialog</t>
+          <t>Day Label；Day Label With Relative</t>
         </is>
       </c>
       <c r="D389" s="7" t="inlineStr">
@@ -10573,7 +10572,7 @@
       </c>
       <c r="E389" s="7" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>{date.monthValue}月{date.dayOfMonth}日 {weekday(date)}</t>
         </is>
       </c>
       <c r="F389" s="5" t="n"/>
@@ -10584,12 +10583,12 @@
       </c>
       <c r="B390" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>Ledger Switcher Dialog</t>
+          <t>Month Label</t>
         </is>
       </c>
       <c r="D390" s="7" t="inlineStr">
@@ -10599,7 +10598,7 @@
       </c>
       <c r="E390" s="7" t="inlineStr">
         <is>
-          <t>切换账本</t>
+          <t>{month.year}年{month.monthValue}月</t>
         </is>
       </c>
       <c r="F390" s="5" t="n"/>
@@ -10610,12 +10609,12 @@
       </c>
       <c r="B391" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Ledger Switcher Dialog</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D391" s="7" t="inlineStr">
@@ -10625,7 +10624,7 @@
       </c>
       <c r="E391" s="7" t="inlineStr">
         <is>
-          <t>当前</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="F391" s="5" t="n"/>
@@ -10636,12 +10635,12 @@
       </c>
       <c r="B392" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C392" s="7" t="inlineStr">
         <is>
-          <t>Ledger Switcher Dialog</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D392" s="7" t="inlineStr">
@@ -10651,7 +10650,7 @@
       </c>
       <c r="E392" s="7" t="inlineStr">
         <is>
-          <t>还没有账本。去「设置 → 账本管理」新建一个。</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="F392" s="5" t="n"/>
@@ -10662,12 +10661,12 @@
       </c>
       <c r="B393" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Month Pager</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D393" s="7" t="inlineStr">
@@ -10677,7 +10676,7 @@
       </c>
       <c r="E393" s="7" t="inlineStr">
         <is>
-          <t>%d 年 %d 月</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="F393" s="5" t="n"/>
@@ -10688,12 +10687,12 @@
       </c>
       <c r="B394" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C394" s="7" t="inlineStr">
         <is>
-          <t>Wheel</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D394" s="7" t="inlineStr">
@@ -10703,7 +10702,7 @@
       </c>
       <c r="E394" s="7" t="inlineStr">
         <is>
-          <t>%02d</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="F394" s="5" t="n"/>
@@ -10714,12 +10713,12 @@
       </c>
       <c r="B395" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Wheel Time Picker Dialog</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D395" s="7" t="inlineStr">
@@ -10729,7 +10728,7 @@
       </c>
       <c r="E395" s="7" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>周六</t>
         </is>
       </c>
       <c r="F395" s="5" t="n"/>
@@ -10740,12 +10739,12 @@
       </c>
       <c r="B396" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C396" s="7" t="inlineStr">
         <is>
-          <t>Wheel Time Picker Dialog</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D396" s="7" t="inlineStr">
@@ -10755,7 +10754,7 @@
       </c>
       <c r="E396" s="7" t="inlineStr">
         <is>
-          <t>当前 %02d:%02d</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="F396" s="5" t="n"/>
@@ -10766,12 +10765,12 @@
       </c>
       <c r="B397" s="7" t="inlineStr">
         <is>
-          <t>通用界面组件</t>
+          <t>日期显示</t>
         </is>
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Wheel Time Picker Dialog</t>
+          <t>WEEKDAYS</t>
         </is>
       </c>
       <c r="D397" s="7" t="inlineStr">
@@ -10781,7 +10780,7 @@
       </c>
       <c r="E397" s="7" t="inlineStr">
         <is>
-          <t>选择时间</t>
+          <t>周日</t>
         </is>
       </c>
       <c r="F397" s="5" t="n"/>
@@ -10792,12 +10791,12 @@
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>金额格式</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Day Label With Relative</t>
+          <t>Format Tiny</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -10807,7 +10806,7 @@
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">今天 · </t>
+          <t>{prefix}{tenths / 10}.{tenths % 10}万</t>
         </is>
       </c>
       <c r="F398" s="5" t="n"/>
@@ -10818,12 +10817,12 @@
       </c>
       <c r="B399" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>金额格式</t>
         </is>
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Day Label With Relative</t>
+          <t>Format Tiny</t>
         </is>
       </c>
       <c r="D399" s="7" t="inlineStr">
@@ -10833,33 +10832,33 @@
       </c>
       <c r="E399" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">明天 · </t>
+          <t>{prefix}{tenths / 10}万</t>
         </is>
       </c>
       <c r="F399" s="5" t="n"/>
     </row>
     <row r="400">
-      <c r="A400" s="6" t="n">
+      <c r="A400" s="3" t="n">
         <v>397</v>
       </c>
-      <c r="B400" s="7" t="inlineStr">
-        <is>
-          <t>日期显示</t>
-        </is>
-      </c>
-      <c r="C400" s="7" t="inlineStr">
-        <is>
-          <t>Day Label With Relative</t>
-        </is>
-      </c>
-      <c r="D400" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E400" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">昨天 · </t>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>系统通知</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="inlineStr">
+        <is>
+          <t>Ensure Channel</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>预算接近上限或已超支时提醒</t>
         </is>
       </c>
       <c r="F400" s="5" t="n"/>
@@ -10870,12 +10869,12 @@
       </c>
       <c r="B401" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>系统通知</t>
         </is>
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Day Label；Day Label With Relative</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="D401" s="7" t="inlineStr">
@@ -10885,7 +10884,7 @@
       </c>
       <c r="E401" s="7" t="inlineStr">
         <is>
-          <t>{date.monthValue}月{date.dayOfMonth}日 {weekday(date)}</t>
+          <t>{alert.name} 已超支</t>
         </is>
       </c>
       <c r="F401" s="5" t="n"/>
@@ -10896,12 +10895,12 @@
       </c>
       <c r="B402" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>系统通知</t>
         </is>
       </c>
       <c r="C402" s="7" t="inlineStr">
         <is>
-          <t>Month Label</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="D402" s="7" t="inlineStr">
@@ -10911,7 +10910,7 @@
       </c>
       <c r="E402" s="7" t="inlineStr">
         <is>
-          <t>{month.year}年{month.monthValue}月</t>
+          <t>{alert.name} 接近上限</t>
         </is>
       </c>
       <c r="F402" s="5" t="n"/>
@@ -10922,12 +10921,12 @@
       </c>
       <c r="B403" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>系统通知</t>
         </is>
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>WEEKDAYS</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="D403" s="7" t="inlineStr">
@@ -10937,7 +10936,7 @@
       </c>
       <c r="E403" s="7" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t xml:space="preserve">已花 {Money.formatWithSymbol(alert.spentCents)} / </t>
         </is>
       </c>
       <c r="F403" s="5" t="n"/>
@@ -10948,12 +10947,12 @@
       </c>
       <c r="B404" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>系统通知</t>
         </is>
       </c>
       <c r="C404" s="7" t="inlineStr">
         <is>
-          <t>WEEKDAYS</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="D404" s="7" t="inlineStr">
@@ -10963,33 +10962,33 @@
       </c>
       <c r="E404" s="7" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t xml:space="preserve">已花 {Money.formatWithSymbol(alert.spentCents)}，超出 </t>
         </is>
       </c>
       <c r="F404" s="5" t="n"/>
     </row>
     <row r="405">
-      <c r="A405" s="6" t="n">
+      <c r="A405" s="3" t="n">
         <v>402</v>
       </c>
-      <c r="B405" s="7" t="inlineStr">
-        <is>
-          <t>日期显示</t>
-        </is>
-      </c>
-      <c r="C405" s="7" t="inlineStr">
-        <is>
-          <t>WEEKDAYS</t>
-        </is>
-      </c>
-      <c r="D405" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E405" s="7" t="inlineStr">
-        <is>
-          <t>周二</t>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>桌面小组件</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="inlineStr">
+        <is>
+          <t>Add Entry Button</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>＋ 记一笔</t>
         </is>
       </c>
       <c r="F405" s="5" t="n"/>
@@ -11000,12 +10999,12 @@
       </c>
       <c r="B406" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>桌面小组件</t>
         </is>
       </c>
       <c r="C406" s="7" t="inlineStr">
         <is>
-          <t>WEEKDAYS</t>
+          <t>Widget Body</t>
         </is>
       </c>
       <c r="D406" s="7" t="inlineStr">
@@ -11015,7 +11014,7 @@
       </c>
       <c r="E406" s="7" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>已花 {Money.format(snapshot.monthExpenseCents)} / {Money.format(snapshot.allowanceCents)}（{(snapshot.progress * 100).toInt()}%）</t>
         </is>
       </c>
       <c r="F406" s="5" t="n"/>
@@ -11026,12 +11025,12 @@
       </c>
       <c r="B407" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>桌面小组件</t>
         </is>
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>WEEKDAYS</t>
+          <t>Widget Body</t>
         </is>
       </c>
       <c r="D407" s="7" t="inlineStr">
@@ -11041,7 +11040,7 @@
       </c>
       <c r="E407" s="7" t="inlineStr">
         <is>
-          <t>周六</t>
+          <t>打开应用以完成初始化</t>
         </is>
       </c>
       <c r="F407" s="5" t="n"/>
@@ -11052,12 +11051,12 @@
       </c>
       <c r="B408" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>桌面小组件</t>
         </is>
       </c>
       <c r="C408" s="7" t="inlineStr">
         <is>
-          <t>WEEKDAYS</t>
+          <t>Widget Body</t>
         </is>
       </c>
       <c r="D408" s="7" t="inlineStr">
@@ -11067,7 +11066,7 @@
       </c>
       <c r="E408" s="7" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>本月支出</t>
         </is>
       </c>
       <c r="F408" s="5" t="n"/>
@@ -11078,48 +11077,48 @@
       </c>
       <c r="B409" s="7" t="inlineStr">
         <is>
-          <t>日期显示</t>
+          <t>桌面小组件</t>
         </is>
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>WEEKDAYS</t>
+          <t>widget_small_description</t>
         </is>
       </c>
       <c r="D409" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>桌面小组件文字</t>
         </is>
       </c>
       <c r="E409" s="7" t="inlineStr">
         <is>
-          <t>周日</t>
+          <t>本月支出或剩余生活费，一键记一笔</t>
         </is>
       </c>
       <c r="F409" s="5" t="n"/>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="n">
+      <c r="A410" s="6" t="n">
         <v>407</v>
       </c>
-      <c r="B410" s="4" t="inlineStr">
-        <is>
-          <t>金额格式</t>
-        </is>
-      </c>
-      <c r="C410" s="4" t="inlineStr">
-        <is>
-          <t>Format Tiny</t>
-        </is>
-      </c>
-      <c r="D410" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E410" s="4" t="inlineStr">
-        <is>
-          <t>{prefix}{tenths / 10}.{tenths % 10}万</t>
+      <c r="B410" s="7" t="inlineStr">
+        <is>
+          <t>桌面小组件</t>
+        </is>
+      </c>
+      <c r="C410" s="7" t="inlineStr">
+        <is>
+          <t>widget_small_label</t>
+        </is>
+      </c>
+      <c r="D410" s="7" t="inlineStr">
+        <is>
+          <t>桌面小组件文字</t>
+        </is>
+      </c>
+      <c r="E410" s="7" t="inlineStr">
+        <is>
+          <t>记账本 · 本月</t>
         </is>
       </c>
       <c r="F410" s="5" t="n"/>
@@ -11130,74 +11129,74 @@
       </c>
       <c r="B411" s="7" t="inlineStr">
         <is>
-          <t>金额格式</t>
+          <t>桌面小组件</t>
         </is>
       </c>
       <c r="C411" s="7" t="inlineStr">
         <is>
-          <t>Format Tiny</t>
+          <t>widget_wide_description</t>
         </is>
       </c>
       <c r="D411" s="7" t="inlineStr">
         <is>
-          <t>界面文字</t>
+          <t>桌面小组件文字</t>
         </is>
       </c>
       <c r="E411" s="7" t="inlineStr">
         <is>
-          <t>{prefix}{tenths / 10}万</t>
+          <t>本月支出、生活费进度，一键记一笔</t>
         </is>
       </c>
       <c r="F411" s="5" t="n"/>
     </row>
     <row r="412">
-      <c r="A412" s="3" t="n">
+      <c r="A412" s="6" t="n">
         <v>409</v>
       </c>
-      <c r="B412" s="4" t="inlineStr">
-        <is>
-          <t>系统通知</t>
-        </is>
-      </c>
-      <c r="C412" s="4" t="inlineStr">
-        <is>
-          <t>Ensure Channel</t>
-        </is>
-      </c>
-      <c r="D412" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E412" s="4" t="inlineStr">
-        <is>
-          <t>预算接近上限或已超支时提醒</t>
+      <c r="B412" s="7" t="inlineStr">
+        <is>
+          <t>桌面小组件</t>
+        </is>
+      </c>
+      <c r="C412" s="7" t="inlineStr">
+        <is>
+          <t>widget_wide_label</t>
+        </is>
+      </c>
+      <c r="D412" s="7" t="inlineStr">
+        <is>
+          <t>桌面小组件文字</t>
+        </is>
+      </c>
+      <c r="E412" s="7" t="inlineStr">
+        <is>
+          <t>记账本 · 本月概览</t>
         </is>
       </c>
       <c r="F412" s="5" t="n"/>
     </row>
     <row r="413">
-      <c r="A413" s="6" t="n">
+      <c r="A413" s="3" t="n">
         <v>410</v>
       </c>
-      <c r="B413" s="7" t="inlineStr">
-        <is>
-          <t>系统通知</t>
-        </is>
-      </c>
-      <c r="C413" s="7" t="inlineStr">
-        <is>
-          <t>Post</t>
-        </is>
-      </c>
-      <c r="D413" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E413" s="7" t="inlineStr">
-        <is>
-          <t>{alert.name} 已超支</t>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>预置数据（首次安装写入数据库）</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="inlineStr">
+        <is>
+          <t>ALIPAY_LEGACY_NAME；账户 · ACCOUNT_TYPES；账户 · Account Type Label</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F413" s="5" t="n"/>
@@ -11208,12 +11207,12 @@
       </c>
       <c r="B414" s="7" t="inlineStr">
         <is>
-          <t>系统通知</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C414" s="7" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>ALIPAY_NAME</t>
         </is>
       </c>
       <c r="D414" s="7" t="inlineStr">
@@ -11223,7 +11222,7 @@
       </c>
       <c r="E414" s="7" t="inlineStr">
         <is>
-          <t>{alert.name} 接近上限</t>
+          <t>支付宝余额</t>
         </is>
       </c>
       <c r="F414" s="5" t="n"/>
@@ -11234,12 +11233,12 @@
       </c>
       <c r="B415" s="7" t="inlineStr">
         <is>
-          <t>系统通知</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>BUDGET_ACCOUNTS</t>
         </is>
       </c>
       <c r="D415" s="7" t="inlineStr">
@@ -11249,7 +11248,7 @@
       </c>
       <c r="E415" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">已花 {Money.formatWithSymbol(alert.spentCents)} / </t>
+          <t>储蓄卡</t>
         </is>
       </c>
       <c r="F415" s="5" t="n"/>
@@ -11260,12 +11259,12 @@
       </c>
       <c r="B416" s="7" t="inlineStr">
         <is>
-          <t>系统通知</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C416" s="7" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>BUDGET_ACCOUNTS</t>
         </is>
       </c>
       <c r="D416" s="7" t="inlineStr">
@@ -11275,33 +11274,33 @@
       </c>
       <c r="E416" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">已花 {Money.formatWithSymbol(alert.spentCents)}，超出 </t>
+          <t>微信零钱</t>
         </is>
       </c>
       <c r="F416" s="5" t="n"/>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="n">
+      <c r="A417" s="6" t="n">
         <v>414</v>
       </c>
-      <c r="B417" s="4" t="inlineStr">
-        <is>
-          <t>桌面小组件</t>
-        </is>
-      </c>
-      <c r="C417" s="4" t="inlineStr">
-        <is>
-          <t>Add Entry Button</t>
-        </is>
-      </c>
-      <c r="D417" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E417" s="4" t="inlineStr">
-        <is>
-          <t>＋ 记一笔</t>
+      <c r="B417" s="7" t="inlineStr">
+        <is>
+          <t>预置数据（首次安装写入数据库）</t>
+        </is>
+      </c>
+      <c r="C417" s="7" t="inlineStr">
+        <is>
+          <t>BUDGET_ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="D417" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E417" s="7" t="inlineStr">
+        <is>
+          <t>校园卡</t>
         </is>
       </c>
       <c r="F417" s="5" t="n"/>
@@ -11312,12 +11311,12 @@
       </c>
       <c r="B418" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C418" s="7" t="inlineStr">
         <is>
-          <t>Widget Body</t>
+          <t>BUDGET_ACCOUNTS；账户 · ACCOUNT_TYPES；账户 · Account Type Label</t>
         </is>
       </c>
       <c r="D418" s="7" t="inlineStr">
@@ -11327,7 +11326,7 @@
       </c>
       <c r="E418" s="7" t="inlineStr">
         <is>
-          <t>已花 {Money.format(snapshot.monthExpenseCents)} / {Money.format(snapshot.allowanceCents)}（{(snapshot.progress * 100).toInt()}%）</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F418" s="5" t="n"/>
@@ -11338,12 +11337,12 @@
       </c>
       <c r="B419" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Widget Body</t>
+          <t>DEFAULT_LEDGER_NAME</t>
         </is>
       </c>
       <c r="D419" s="7" t="inlineStr">
@@ -11353,7 +11352,7 @@
       </c>
       <c r="E419" s="7" t="inlineStr">
         <is>
-          <t>打开应用以完成初始化</t>
+          <t>我的账本</t>
         </is>
       </c>
       <c r="F419" s="5" t="n"/>
@@ -11364,12 +11363,12 @@
       </c>
       <c r="B420" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C420" s="7" t="inlineStr">
         <is>
-          <t>Widget Body</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D420" s="7" t="inlineStr">
@@ -11379,7 +11378,7 @@
       </c>
       <c r="E420" s="7" t="inlineStr">
         <is>
-          <t>本月支出</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="F420" s="5" t="n"/>
@@ -11390,22 +11389,22 @@
       </c>
       <c r="B421" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>widget_small_description</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D421" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件文字</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E421" s="7" t="inlineStr">
         <is>
-          <t>本月支出或剩余生活费，一键记一笔</t>
+          <t>人情</t>
         </is>
       </c>
       <c r="F421" s="5" t="n"/>
@@ -11416,22 +11415,22 @@
       </c>
       <c r="B422" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C422" s="7" t="inlineStr">
         <is>
-          <t>widget_small_label</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D422" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件文字</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E422" s="7" t="inlineStr">
         <is>
-          <t>记账本 · 本月</t>
+          <t>会员订阅</t>
         </is>
       </c>
       <c r="F422" s="5" t="n"/>
@@ -11442,22 +11441,22 @@
       </c>
       <c r="B423" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>widget_wide_description</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D423" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件文字</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E423" s="7" t="inlineStr">
         <is>
-          <t>本月支出、生活费进度，一键记一笔</t>
+          <t>住院</t>
         </is>
       </c>
       <c r="F423" s="5" t="n"/>
@@ -11468,48 +11467,48 @@
       </c>
       <c r="B424" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件</t>
+          <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
       <c r="C424" s="7" t="inlineStr">
         <is>
-          <t>widget_wide_label</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D424" s="7" t="inlineStr">
         <is>
-          <t>桌面小组件文字</t>
+          <t>界面文字</t>
         </is>
       </c>
       <c r="E424" s="7" t="inlineStr">
         <is>
-          <t>记账本 · 本月概览</t>
+          <t>体检</t>
         </is>
       </c>
       <c r="F424" s="5" t="n"/>
     </row>
     <row r="425">
-      <c r="A425" s="3" t="n">
+      <c r="A425" s="6" t="n">
         <v>422</v>
       </c>
-      <c r="B425" s="4" t="inlineStr">
+      <c r="B425" s="7" t="inlineStr">
         <is>
           <t>预置数据（首次安装写入数据库）</t>
         </is>
       </c>
-      <c r="C425" s="4" t="inlineStr">
-        <is>
-          <t>ALIPAY_LEGACY_NAME；账户 · ACCOUNT_TYPES；账户 · Account Type Label</t>
-        </is>
-      </c>
-      <c r="D425" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E425" s="4" t="inlineStr">
-        <is>
-          <t>支付宝</t>
+      <c r="C425" s="7" t="inlineStr">
+        <is>
+          <t>EXPENSE_TREE</t>
+        </is>
+      </c>
+      <c r="D425" s="7" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E425" s="7" t="inlineStr">
+        <is>
+          <t>保险</t>
         </is>
       </c>
       <c r="F425" s="5" t="n"/>
@@ -11525,7 +11524,7 @@
       </c>
       <c r="C426" s="7" t="inlineStr">
         <is>
-          <t>ALIPAY_NAME</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D426" s="7" t="inlineStr">
@@ -11535,7 +11534,7 @@
       </c>
       <c r="E426" s="7" t="inlineStr">
         <is>
-          <t>支付宝余额</t>
+          <t>停车</t>
         </is>
       </c>
       <c r="F426" s="5" t="n"/>
@@ -11551,7 +11550,7 @@
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>BUDGET_ACCOUNTS</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D427" s="7" t="inlineStr">
@@ -11561,7 +11560,7 @@
       </c>
       <c r="E427" s="7" t="inlineStr">
         <is>
-          <t>储蓄卡</t>
+          <t>共享单车</t>
         </is>
       </c>
       <c r="F427" s="5" t="n"/>
@@ -11577,7 +11576,7 @@
       </c>
       <c r="C428" s="7" t="inlineStr">
         <is>
-          <t>BUDGET_ACCOUNTS</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D428" s="7" t="inlineStr">
@@ -11587,7 +11586,7 @@
       </c>
       <c r="E428" s="7" t="inlineStr">
         <is>
-          <t>微信零钱</t>
+          <t>兴趣</t>
         </is>
       </c>
       <c r="F428" s="5" t="n"/>
@@ -11603,7 +11602,7 @@
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>BUDGET_ACCOUNTS</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D429" s="7" t="inlineStr">
@@ -11613,7 +11612,7 @@
       </c>
       <c r="E429" s="7" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>其他支出</t>
         </is>
       </c>
       <c r="F429" s="5" t="n"/>
@@ -11629,7 +11628,7 @@
       </c>
       <c r="C430" s="7" t="inlineStr">
         <is>
-          <t>BUDGET_ACCOUNTS；账户 · ACCOUNT_TYPES；账户 · Account Type Label</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D430" s="7" t="inlineStr">
@@ -11639,7 +11638,7 @@
       </c>
       <c r="E430" s="7" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>利息</t>
         </is>
       </c>
       <c r="F430" s="5" t="n"/>
@@ -11655,7 +11654,7 @@
       </c>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>DEFAULT_LEDGER_NAME</t>
+          <t>EXPENSE_TREE</t>
         </is>
       </c>
       <c r="D431" s="7" t="inlineStr">
@@ -11665,7 +11664,7 @@
       </c>
       <c r="E431" s="7" t="inlineStr">
         <is>
-          <t>我的账本</t>
+          <t>办公用品</t>
         </is>
       </c>
       <c r="F431" s="5" t="n"/>
@@ -11691,7 +11690,7 @@
       </c>
       <c r="E432" s="7" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>加油</t>
         </is>
       </c>
       <c r="F432" s="5" t="n"/>
@@ -11717,7 +11716,7 @@
       </c>
       <c r="E433" s="7" t="inlineStr">
         <is>
-          <t>人情</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="F433" s="5" t="n"/>
@@ -11743,7 +11742,7 @@
       </c>
       <c r="E434" s="7" t="inlineStr">
         <is>
-          <t>会员订阅</t>
+          <t>取暖费</t>
         </is>
       </c>
       <c r="F434" s="5" t="n"/>
@@ -11769,7 +11768,7 @@
       </c>
       <c r="E435" s="7" t="inlineStr">
         <is>
-          <t>住院</t>
+          <t>咖啡/茶饮</t>
         </is>
       </c>
       <c r="F435" s="5" t="n"/>
@@ -11795,7 +11794,7 @@
       </c>
       <c r="E436" s="7" t="inlineStr">
         <is>
-          <t>体检</t>
+          <t>培训</t>
         </is>
       </c>
       <c r="F436" s="5" t="n"/>
@@ -11821,7 +11820,7 @@
       </c>
       <c r="E437" s="7" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>娱乐</t>
         </is>
       </c>
       <c r="F437" s="5" t="n"/>
@@ -11847,7 +11846,7 @@
       </c>
       <c r="E438" s="7" t="inlineStr">
         <is>
-          <t>停车</t>
+          <t>孝敬长辈</t>
         </is>
       </c>
       <c r="F438" s="5" t="n"/>
@@ -11873,7 +11872,7 @@
       </c>
       <c r="E439" s="7" t="inlineStr">
         <is>
-          <t>共享单车</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="F439" s="5" t="n"/>
@@ -11899,7 +11898,7 @@
       </c>
       <c r="E440" s="7" t="inlineStr">
         <is>
-          <t>兴趣</t>
+          <t>宠物</t>
         </is>
       </c>
       <c r="F440" s="5" t="n"/>
@@ -11925,7 +11924,7 @@
       </c>
       <c r="E441" s="7" t="inlineStr">
         <is>
-          <t>其他支出</t>
+          <t>宠物医疗</t>
         </is>
       </c>
       <c r="F441" s="5" t="n"/>
@@ -11951,7 +11950,7 @@
       </c>
       <c r="E442" s="7" t="inlineStr">
         <is>
-          <t>利息</t>
+          <t>宠物用品</t>
         </is>
       </c>
       <c r="F442" s="5" t="n"/>
@@ -11977,7 +11976,7 @@
       </c>
       <c r="E443" s="7" t="inlineStr">
         <is>
-          <t>办公用品</t>
+          <t>宠物粮食</t>
         </is>
       </c>
       <c r="F443" s="5" t="n"/>
@@ -12003,7 +12002,7 @@
       </c>
       <c r="E444" s="7" t="inlineStr">
         <is>
-          <t>加油</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="F444" s="5" t="n"/>
@@ -12029,7 +12028,7 @@
       </c>
       <c r="E445" s="7" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="F445" s="5" t="n"/>
@@ -12055,7 +12054,7 @@
       </c>
       <c r="E446" s="7" t="inlineStr">
         <is>
-          <t>取暖费</t>
+          <t>宽带</t>
         </is>
       </c>
       <c r="F446" s="5" t="n"/>
@@ -12081,7 +12080,7 @@
       </c>
       <c r="E447" s="7" t="inlineStr">
         <is>
-          <t>咖啡/茶饮</t>
+          <t>居住</t>
         </is>
       </c>
       <c r="F447" s="5" t="n"/>
@@ -12107,7 +12106,7 @@
       </c>
       <c r="E448" s="7" t="inlineStr">
         <is>
-          <t>培训</t>
+          <t>工作</t>
         </is>
       </c>
       <c r="F448" s="5" t="n"/>
@@ -12133,7 +12132,7 @@
       </c>
       <c r="E449" s="7" t="inlineStr">
         <is>
-          <t>娱乐</t>
+          <t>差旅</t>
         </is>
       </c>
       <c r="F449" s="5" t="n"/>
@@ -12159,7 +12158,7 @@
       </c>
       <c r="E450" s="7" t="inlineStr">
         <is>
-          <t>孝敬长辈</t>
+          <t>影视</t>
         </is>
       </c>
       <c r="F450" s="5" t="n"/>
@@ -12185,7 +12184,7 @@
       </c>
       <c r="E451" s="7" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>快递</t>
         </is>
       </c>
       <c r="F451" s="5" t="n"/>
@@ -12211,7 +12210,7 @@
       </c>
       <c r="E452" s="7" t="inlineStr">
         <is>
-          <t>宠物</t>
+          <t>房贷</t>
         </is>
       </c>
       <c r="F452" s="5" t="n"/>
@@ -12237,7 +12236,7 @@
       </c>
       <c r="E453" s="7" t="inlineStr">
         <is>
-          <t>宠物医疗</t>
+          <t>打印</t>
         </is>
       </c>
       <c r="F453" s="5" t="n"/>
@@ -12263,7 +12262,7 @@
       </c>
       <c r="E454" s="7" t="inlineStr">
         <is>
-          <t>宠物用品</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="F454" s="5" t="n"/>
@@ -12289,7 +12288,7 @@
       </c>
       <c r="E455" s="7" t="inlineStr">
         <is>
-          <t>宠物粮食</t>
+          <t>文具</t>
         </is>
       </c>
       <c r="F455" s="5" t="n"/>
@@ -12315,7 +12314,7 @@
       </c>
       <c r="E456" s="7" t="inlineStr">
         <is>
-          <t>家居</t>
+          <t>旅行</t>
         </is>
       </c>
       <c r="F456" s="5" t="n"/>
@@ -12341,7 +12340,7 @@
       </c>
       <c r="E457" s="7" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="F457" s="5" t="n"/>
@@ -12367,7 +12366,7 @@
       </c>
       <c r="E458" s="7" t="inlineStr">
         <is>
-          <t>宽带</t>
+          <t>校园</t>
         </is>
       </c>
       <c r="F458" s="5" t="n"/>
@@ -12393,7 +12392,7 @@
       </c>
       <c r="E459" s="7" t="inlineStr">
         <is>
-          <t>居住</t>
+          <t>校园卡充值</t>
         </is>
       </c>
       <c r="F459" s="5" t="n"/>
@@ -12419,7 +12418,7 @@
       </c>
       <c r="E460" s="7" t="inlineStr">
         <is>
-          <t>工作</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="F460" s="5" t="n"/>
@@ -12445,7 +12444,7 @@
       </c>
       <c r="E461" s="7" t="inlineStr">
         <is>
-          <t>差旅</t>
+          <t>水费</t>
         </is>
       </c>
       <c r="F461" s="5" t="n"/>
@@ -12471,7 +12470,7 @@
       </c>
       <c r="E462" s="7" t="inlineStr">
         <is>
-          <t>影视</t>
+          <t>流量</t>
         </is>
       </c>
       <c r="F462" s="5" t="n"/>
@@ -12497,7 +12496,7 @@
       </c>
       <c r="E463" s="7" t="inlineStr">
         <is>
-          <t>快递</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="F463" s="5" t="n"/>
@@ -12523,7 +12522,7 @@
       </c>
       <c r="E464" s="7" t="inlineStr">
         <is>
-          <t>房贷</t>
+          <t>演出</t>
         </is>
       </c>
       <c r="F464" s="5" t="n"/>
@@ -12549,7 +12548,7 @@
       </c>
       <c r="E465" s="7" t="inlineStr">
         <is>
-          <t>打印</t>
+          <t>火车/高铁</t>
         </is>
       </c>
       <c r="F465" s="5" t="n"/>
@@ -12575,7 +12574,7 @@
       </c>
       <c r="E466" s="7" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>燃气费</t>
         </is>
       </c>
       <c r="F466" s="5" t="n"/>
@@ -12601,7 +12600,7 @@
       </c>
       <c r="E467" s="7" t="inlineStr">
         <is>
-          <t>文具</t>
+          <t>牙科</t>
         </is>
       </c>
       <c r="F467" s="5" t="n"/>
@@ -12627,7 +12626,7 @@
       </c>
       <c r="E468" s="7" t="inlineStr">
         <is>
-          <t>旅行</t>
+          <t>物业</t>
         </is>
       </c>
       <c r="F468" s="5" t="n"/>
@@ -12653,7 +12652,7 @@
       </c>
       <c r="E469" s="7" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>班费</t>
         </is>
       </c>
       <c r="F469" s="5" t="n"/>
@@ -12679,7 +12678,7 @@
       </c>
       <c r="E470" s="7" t="inlineStr">
         <is>
-          <t>校园</t>
+          <t>电费</t>
         </is>
       </c>
       <c r="F470" s="5" t="n"/>
@@ -12705,7 +12704,7 @@
       </c>
       <c r="E471" s="7" t="inlineStr">
         <is>
-          <t>校园卡充值</t>
+          <t>礼物</t>
         </is>
       </c>
       <c r="F471" s="5" t="n"/>
@@ -12731,7 +12730,7 @@
       </c>
       <c r="E472" s="7" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>社团</t>
         </is>
       </c>
       <c r="F472" s="5" t="n"/>
@@ -12757,7 +12756,7 @@
       </c>
       <c r="E473" s="7" t="inlineStr">
         <is>
-          <t>水费</t>
+          <t>税费</t>
         </is>
       </c>
       <c r="F473" s="5" t="n"/>
@@ -12783,7 +12782,7 @@
       </c>
       <c r="E474" s="7" t="inlineStr">
         <is>
-          <t>流量</t>
+          <t>红包</t>
         </is>
       </c>
       <c r="F474" s="5" t="n"/>
@@ -12809,7 +12808,7 @@
       </c>
       <c r="E475" s="7" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="F475" s="5" t="n"/>
@@ -12835,7 +12834,7 @@
       </c>
       <c r="E476" s="7" t="inlineStr">
         <is>
-          <t>演出</t>
+          <t>考试报名</t>
         </is>
       </c>
       <c r="F476" s="5" t="n"/>
@@ -12861,7 +12860,7 @@
       </c>
       <c r="E477" s="7" t="inlineStr">
         <is>
-          <t>火车/高铁</t>
+          <t>聚餐</t>
         </is>
       </c>
       <c r="F477" s="5" t="n"/>
@@ -12887,7 +12886,7 @@
       </c>
       <c r="E478" s="7" t="inlineStr">
         <is>
-          <t>燃气费</t>
+          <t>药品</t>
         </is>
       </c>
       <c r="F478" s="5" t="n"/>
@@ -12913,7 +12912,7 @@
       </c>
       <c r="E479" s="7" t="inlineStr">
         <is>
-          <t>牙科</t>
+          <t>请客</t>
         </is>
       </c>
       <c r="F479" s="5" t="n"/>
@@ -12939,7 +12938,7 @@
       </c>
       <c r="E480" s="7" t="inlineStr">
         <is>
-          <t>物业</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="F480" s="5" t="n"/>
@@ -12965,7 +12964,7 @@
       </c>
       <c r="E481" s="7" t="inlineStr">
         <is>
-          <t>班费</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="F481" s="5" t="n"/>
@@ -12991,7 +12990,7 @@
       </c>
       <c r="E482" s="7" t="inlineStr">
         <is>
-          <t>电费</t>
+          <t>运动健身</t>
         </is>
       </c>
       <c r="F482" s="5" t="n"/>
@@ -13017,7 +13016,7 @@
       </c>
       <c r="E483" s="7" t="inlineStr">
         <is>
-          <t>礼物</t>
+          <t>通讯</t>
         </is>
       </c>
       <c r="F483" s="5" t="n"/>
@@ -13043,7 +13042,7 @@
       </c>
       <c r="E484" s="7" t="inlineStr">
         <is>
-          <t>社团</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="F484" s="5" t="n"/>
@@ -13069,7 +13068,7 @@
       </c>
       <c r="E485" s="7" t="inlineStr">
         <is>
-          <t>税费</t>
+          <t>门诊</t>
         </is>
       </c>
       <c r="F485" s="5" t="n"/>
@@ -13095,7 +13094,7 @@
       </c>
       <c r="E486" s="7" t="inlineStr">
         <is>
-          <t>红包</t>
+          <t>飞机</t>
         </is>
       </c>
       <c r="F486" s="5" t="n"/>
@@ -13121,7 +13120,7 @@
       </c>
       <c r="E487" s="7" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>餐饮</t>
         </is>
       </c>
       <c r="F487" s="5" t="n"/>
@@ -13137,7 +13136,7 @@
       </c>
       <c r="C488" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D488" s="7" t="inlineStr">
@@ -13147,7 +13146,7 @@
       </c>
       <c r="E488" s="7" t="inlineStr">
         <is>
-          <t>考试报名</t>
+          <t>公共交通</t>
         </is>
       </c>
       <c r="F488" s="5" t="n"/>
@@ -13163,7 +13162,7 @@
       </c>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D489" s="7" t="inlineStr">
@@ -13173,7 +13172,7 @@
       </c>
       <c r="E489" s="7" t="inlineStr">
         <is>
-          <t>聚餐</t>
+          <t>午餐</t>
         </is>
       </c>
       <c r="F489" s="5" t="n"/>
@@ -13189,7 +13188,7 @@
       </c>
       <c r="C490" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D490" s="7" t="inlineStr">
@@ -13199,7 +13198,7 @@
       </c>
       <c r="E490" s="7" t="inlineStr">
         <is>
-          <t>药品</t>
+          <t>外卖</t>
         </is>
       </c>
       <c r="F490" s="5" t="n"/>
@@ -13215,7 +13214,7 @@
       </c>
       <c r="C491" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D491" s="7" t="inlineStr">
@@ -13225,7 +13224,7 @@
       </c>
       <c r="E491" s="7" t="inlineStr">
         <is>
-          <t>请客</t>
+          <t>房租</t>
         </is>
       </c>
       <c r="F491" s="5" t="n"/>
@@ -13241,7 +13240,7 @@
       </c>
       <c r="C492" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D492" s="7" t="inlineStr">
@@ -13251,7 +13250,7 @@
       </c>
       <c r="E492" s="7" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>打车</t>
         </is>
       </c>
       <c r="F492" s="5" t="n"/>
@@ -13267,7 +13266,7 @@
       </c>
       <c r="C493" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D493" s="7" t="inlineStr">
@@ -13277,7 +13276,7 @@
       </c>
       <c r="E493" s="7" t="inlineStr">
         <is>
-          <t>过路费</t>
+          <t>教材</t>
         </is>
       </c>
       <c r="F493" s="5" t="n"/>
@@ -13293,7 +13292,7 @@
       </c>
       <c r="C494" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D494" s="7" t="inlineStr">
@@ -13303,7 +13302,7 @@
       </c>
       <c r="E494" s="7" t="inlineStr">
         <is>
-          <t>运动健身</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="F494" s="5" t="n"/>
@@ -13319,7 +13318,7 @@
       </c>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D495" s="7" t="inlineStr">
@@ -13329,7 +13328,7 @@
       </c>
       <c r="E495" s="7" t="inlineStr">
         <is>
-          <t>通讯</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="F495" s="5" t="n"/>
@@ -13345,7 +13344,7 @@
       </c>
       <c r="C496" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D496" s="7" t="inlineStr">
@@ -13355,7 +13354,7 @@
       </c>
       <c r="E496" s="7" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>晚餐</t>
         </is>
       </c>
       <c r="F496" s="5" t="n"/>
@@ -13371,7 +13370,7 @@
       </c>
       <c r="C497" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D497" s="7" t="inlineStr">
@@ -13381,7 +13380,7 @@
       </c>
       <c r="E497" s="7" t="inlineStr">
         <is>
-          <t>门诊</t>
+          <t>话费</t>
         </is>
       </c>
       <c r="F497" s="5" t="n"/>
@@ -13397,7 +13396,7 @@
       </c>
       <c r="C498" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D498" s="7" t="inlineStr">
@@ -13407,7 +13406,7 @@
       </c>
       <c r="E498" s="7" t="inlineStr">
         <is>
-          <t>飞机</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="F498" s="5" t="n"/>
@@ -13423,7 +13422,7 @@
       </c>
       <c r="C499" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE</t>
+          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
         </is>
       </c>
       <c r="D499" s="7" t="inlineStr">
@@ -13433,7 +13432,7 @@
       </c>
       <c r="E499" s="7" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="F499" s="5" t="n"/>
@@ -13449,7 +13448,7 @@
       </c>
       <c r="C500" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>EXPENSE_TREE；账单详情 · Fields Card；记账页 · Monthly Panel</t>
         </is>
       </c>
       <c r="D500" s="7" t="inlineStr">
@@ -13459,7 +13458,7 @@
       </c>
       <c r="E500" s="7" t="inlineStr">
         <is>
-          <t>公共交通</t>
+          <t>手续费</t>
         </is>
       </c>
       <c r="F500" s="5" t="n"/>
@@ -13475,7 +13474,7 @@
       </c>
       <c r="C501" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>EXPENSE_TREE；账户 · ACCOUNT_TYPES；账户 · Account Type Label 等4处</t>
         </is>
       </c>
       <c r="D501" s="7" t="inlineStr">
@@ -13485,7 +13484,7 @@
       </c>
       <c r="E501" s="7" t="inlineStr">
         <is>
-          <t>午餐</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F501" s="5" t="n"/>
@@ -13501,7 +13500,7 @@
       </c>
       <c r="C502" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>HIDDEN_ACCOUNT_NAME</t>
         </is>
       </c>
       <c r="D502" s="7" t="inlineStr">
@@ -13511,7 +13510,7 @@
       </c>
       <c r="E502" s="7" t="inlineStr">
         <is>
-          <t>外卖</t>
+          <t>累计账户</t>
         </is>
       </c>
       <c r="F502" s="5" t="n"/>
@@ -13527,7 +13526,7 @@
       </c>
       <c r="C503" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>INCOME_ITEMS</t>
         </is>
       </c>
       <c r="D503" s="7" t="inlineStr">
@@ -13537,7 +13536,7 @@
       </c>
       <c r="E503" s="7" t="inlineStr">
         <is>
-          <t>房租</t>
+          <t>二手变卖</t>
         </is>
       </c>
       <c r="F503" s="5" t="n"/>
@@ -13553,7 +13552,7 @@
       </c>
       <c r="C504" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>INCOME_ITEMS</t>
         </is>
       </c>
       <c r="D504" s="7" t="inlineStr">
@@ -13563,7 +13562,7 @@
       </c>
       <c r="E504" s="7" t="inlineStr">
         <is>
-          <t>打车</t>
+          <t>兼职/实习</t>
         </is>
       </c>
       <c r="F504" s="5" t="n"/>
@@ -13579,7 +13578,7 @@
       </c>
       <c r="C505" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>INCOME_ITEMS</t>
         </is>
       </c>
       <c r="D505" s="7" t="inlineStr">
@@ -13589,7 +13588,7 @@
       </c>
       <c r="E505" s="7" t="inlineStr">
         <is>
-          <t>教材</t>
+          <t>奖学金/助学金</t>
         </is>
       </c>
       <c r="F505" s="5" t="n"/>
@@ -13605,7 +13604,7 @@
       </c>
       <c r="C506" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>INCOME_ITEMS</t>
         </is>
       </c>
       <c r="D506" s="7" t="inlineStr">
@@ -13615,7 +13614,7 @@
       </c>
       <c r="E506" s="7" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>报销</t>
         </is>
       </c>
       <c r="F506" s="5" t="n"/>
@@ -13631,7 +13630,7 @@
       </c>
       <c r="C507" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>INCOME_ITEMS</t>
         </is>
       </c>
       <c r="D507" s="7" t="inlineStr">
@@ -13641,7 +13640,7 @@
       </c>
       <c r="E507" s="7" t="inlineStr">
         <is>
-          <t>早餐</t>
+          <t>生活费</t>
         </is>
       </c>
       <c r="F507" s="5" t="n"/>
@@ -13657,7 +13656,7 @@
       </c>
       <c r="C508" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>INCOME_ITEMS</t>
         </is>
       </c>
       <c r="D508" s="7" t="inlineStr">
@@ -13667,33 +13666,33 @@
       </c>
       <c r="E508" s="7" t="inlineStr">
         <is>
-          <t>晚餐</t>
+          <t>红包/亲友转账</t>
         </is>
       </c>
       <c r="F508" s="5" t="n"/>
     </row>
     <row r="509">
-      <c r="A509" s="6" t="n">
+      <c r="A509" s="3" t="n">
         <v>506</v>
       </c>
-      <c r="B509" s="7" t="inlineStr">
-        <is>
-          <t>预置数据（首次安装写入数据库）</t>
-        </is>
-      </c>
-      <c r="C509" s="7" t="inlineStr">
-        <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
-        </is>
-      </c>
-      <c r="D509" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E509" s="7" t="inlineStr">
-        <is>
-          <t>话费</t>
+      <c r="B509" s="4" t="inlineStr">
+        <is>
+          <t>备份与恢复</t>
+        </is>
+      </c>
+      <c r="C509" s="4" t="inlineStr">
+        <is>
+          <t>Bind</t>
+        </is>
+      </c>
+      <c r="D509" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E509" s="4" t="inlineStr">
+        <is>
+          <t>备份里有一行不是简单值。</t>
         </is>
       </c>
       <c r="F509" s="5" t="n"/>
@@ -13704,12 +13703,12 @@
       </c>
       <c r="B510" s="7" t="inlineStr">
         <is>
-          <t>预置数据（首次安装写入数据库）</t>
+          <t>备份与恢复</t>
         </is>
       </c>
       <c r="C510" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>Read Cell</t>
         </is>
       </c>
       <c r="D510" s="7" t="inlineStr">
@@ -13719,7 +13718,7 @@
       </c>
       <c r="E510" s="7" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>表里有二进制字段，备份暂不支持。</t>
         </is>
       </c>
       <c r="F510" s="5" t="n"/>
@@ -13730,12 +13729,12 @@
       </c>
       <c r="B511" s="7" t="inlineStr">
         <is>
-          <t>预置数据（首次安装写入数据库）</t>
+          <t>备份与恢复</t>
         </is>
       </c>
       <c r="C511" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；记账页常用类别 · NAMES</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D511" s="7" t="inlineStr">
@@ -13745,7 +13744,7 @@
       </c>
       <c r="E511" s="7" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>备份来自 v{file.schemaVersion} 的数据结构，当前是 v{expectedSchemaVersion}，不能直接恢复。</t>
         </is>
       </c>
       <c r="F511" s="5" t="n"/>
@@ -13756,12 +13755,12 @@
       </c>
       <c r="B512" s="7" t="inlineStr">
         <is>
-          <t>预置数据（首次安装写入数据库）</t>
+          <t>备份与恢复</t>
         </is>
       </c>
       <c r="C512" s="7" t="inlineStr">
         <is>
-          <t>EXPENSE_TREE；账单详情 · Fields Card；记账页 · Monthly Panel</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D512" s="7" t="inlineStr">
@@ -13771,33 +13770,33 @@
       </c>
       <c r="E512" s="7" t="inlineStr">
         <is>
-          <t>手续费</t>
+          <t>备份里有当前版本不存在的表：{missing.joinToString()}。</t>
         </is>
       </c>
       <c r="F512" s="5" t="n"/>
     </row>
     <row r="513">
-      <c r="A513" s="6" t="n">
+      <c r="A513" s="3" t="n">
         <v>510</v>
       </c>
-      <c r="B513" s="7" t="inlineStr">
-        <is>
-          <t>预置数据（首次安装写入数据库）</t>
-        </is>
-      </c>
-      <c r="C513" s="7" t="inlineStr">
-        <is>
-          <t>EXPENSE_TREE；账户 · ACCOUNT_TYPES；账户 · Account Type Label 等4处</t>
-        </is>
-      </c>
-      <c r="D513" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E513" s="7" t="inlineStr">
-        <is>
-          <t>其他</t>
+      <c r="B513" s="4" t="inlineStr">
+        <is>
+          <t>月付自动扣款</t>
+        </is>
+      </c>
+      <c r="C513" s="4" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="D513" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E513" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 期</t>
         </is>
       </c>
       <c r="F513" s="5" t="n"/>
@@ -13808,12 +13807,12 @@
       </c>
       <c r="B514" s="7" t="inlineStr">
         <is>
-          <t>预置数据（首次安装写入数据库）</t>
+          <t>月付自动扣款</t>
         </is>
       </c>
       <c r="C514" s="7" t="inlineStr">
         <is>
-          <t>HIDDEN_ACCOUNT_NAME</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="D514" s="7" t="inlineStr">
@@ -13823,7 +13822,7 @@
       </c>
       <c r="E514" s="7" t="inlineStr">
         <is>
-          <t>累计账户</t>
+          <t xml:space="preserve"> 第 </t>
         </is>
       </c>
       <c r="F514" s="5" t="n"/>
@@ -13834,12 +13833,12 @@
       </c>
       <c r="B515" s="7" t="inlineStr">
         <is>
-          <t>预置数据（首次安装写入数据库）</t>
+          <t>月付自动扣款</t>
         </is>
       </c>
       <c r="C515" s="7" t="inlineStr">
         <is>
-          <t>INCOME_ITEMS</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="D515" s="7" t="inlineStr">
@@ -13849,33 +13848,33 @@
       </c>
       <c r="E515" s="7" t="inlineStr">
         <is>
-          <t>二手变卖</t>
+          <t>（含手续费）</t>
         </is>
       </c>
       <c r="F515" s="5" t="n"/>
     </row>
     <row r="516">
-      <c r="A516" s="6" t="n">
+      <c r="A516" s="3" t="n">
         <v>513</v>
       </c>
-      <c r="B516" s="7" t="inlineStr">
-        <is>
-          <t>预置数据（首次安装写入数据库）</t>
-        </is>
-      </c>
-      <c r="C516" s="7" t="inlineStr">
-        <is>
-          <t>INCOME_ITEMS</t>
-        </is>
-      </c>
-      <c r="D516" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E516" s="7" t="inlineStr">
-        <is>
-          <t>兼职/实习</t>
+      <c r="B516" s="4" t="inlineStr">
+        <is>
+          <t>预算提醒</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="D516" s="4" t="inlineStr">
+        <is>
+          <t>界面文字</t>
+        </is>
+      </c>
+      <c r="E516" s="4" t="inlineStr">
+        <is>
+          <t>分类预算</t>
         </is>
       </c>
       <c r="F516" s="5" t="n"/>
@@ -13886,12 +13885,12 @@
       </c>
       <c r="B517" s="7" t="inlineStr">
         <is>
-          <t>预置数据（首次安装写入数据库）</t>
+          <t>预算提醒</t>
         </is>
       </c>
       <c r="C517" s="7" t="inlineStr">
         <is>
-          <t>INCOME_ITEMS</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="D517" s="7" t="inlineStr">
@@ -13901,325 +13900,13 @@
       </c>
       <c r="E517" s="7" t="inlineStr">
         <is>
-          <t>奖学金/助学金</t>
+          <t>总预算</t>
         </is>
       </c>
       <c r="F517" s="5" t="n"/>
     </row>
-    <row r="518">
-      <c r="A518" s="6" t="n">
-        <v>515</v>
-      </c>
-      <c r="B518" s="7" t="inlineStr">
-        <is>
-          <t>预置数据（首次安装写入数据库）</t>
-        </is>
-      </c>
-      <c r="C518" s="7" t="inlineStr">
-        <is>
-          <t>INCOME_ITEMS</t>
-        </is>
-      </c>
-      <c r="D518" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E518" s="7" t="inlineStr">
-        <is>
-          <t>报销</t>
-        </is>
-      </c>
-      <c r="F518" s="5" t="n"/>
-    </row>
-    <row r="519">
-      <c r="A519" s="6" t="n">
-        <v>516</v>
-      </c>
-      <c r="B519" s="7" t="inlineStr">
-        <is>
-          <t>预置数据（首次安装写入数据库）</t>
-        </is>
-      </c>
-      <c r="C519" s="7" t="inlineStr">
-        <is>
-          <t>INCOME_ITEMS</t>
-        </is>
-      </c>
-      <c r="D519" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E519" s="7" t="inlineStr">
-        <is>
-          <t>生活费</t>
-        </is>
-      </c>
-      <c r="F519" s="5" t="n"/>
-    </row>
-    <row r="520">
-      <c r="A520" s="6" t="n">
-        <v>517</v>
-      </c>
-      <c r="B520" s="7" t="inlineStr">
-        <is>
-          <t>预置数据（首次安装写入数据库）</t>
-        </is>
-      </c>
-      <c r="C520" s="7" t="inlineStr">
-        <is>
-          <t>INCOME_ITEMS</t>
-        </is>
-      </c>
-      <c r="D520" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E520" s="7" t="inlineStr">
-        <is>
-          <t>红包/亲友转账</t>
-        </is>
-      </c>
-      <c r="F520" s="5" t="n"/>
-    </row>
-    <row r="521">
-      <c r="A521" s="3" t="n">
-        <v>518</v>
-      </c>
-      <c r="B521" s="4" t="inlineStr">
-        <is>
-          <t>备份与恢复</t>
-        </is>
-      </c>
-      <c r="C521" s="4" t="inlineStr">
-        <is>
-          <t>Bind</t>
-        </is>
-      </c>
-      <c r="D521" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E521" s="4" t="inlineStr">
-        <is>
-          <t>备份里有一行不是简单值。</t>
-        </is>
-      </c>
-      <c r="F521" s="5" t="n"/>
-    </row>
-    <row r="522">
-      <c r="A522" s="6" t="n">
-        <v>519</v>
-      </c>
-      <c r="B522" s="7" t="inlineStr">
-        <is>
-          <t>备份与恢复</t>
-        </is>
-      </c>
-      <c r="C522" s="7" t="inlineStr">
-        <is>
-          <t>Read Cell</t>
-        </is>
-      </c>
-      <c r="D522" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E522" s="7" t="inlineStr">
-        <is>
-          <t>表里有二进制字段，备份暂不支持。</t>
-        </is>
-      </c>
-      <c r="F522" s="5" t="n"/>
-    </row>
-    <row r="523">
-      <c r="A523" s="6" t="n">
-        <v>520</v>
-      </c>
-      <c r="B523" s="7" t="inlineStr">
-        <is>
-          <t>备份与恢复</t>
-        </is>
-      </c>
-      <c r="C523" s="7" t="inlineStr">
-        <is>
-          <t>Restore</t>
-        </is>
-      </c>
-      <c r="D523" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E523" s="7" t="inlineStr">
-        <is>
-          <t>备份来自 v{file.schemaVersion} 的数据结构，当前是 v{expectedSchemaVersion}，不能直接恢复。</t>
-        </is>
-      </c>
-      <c r="F523" s="5" t="n"/>
-    </row>
-    <row r="524">
-      <c r="A524" s="6" t="n">
-        <v>521</v>
-      </c>
-      <c r="B524" s="7" t="inlineStr">
-        <is>
-          <t>备份与恢复</t>
-        </is>
-      </c>
-      <c r="C524" s="7" t="inlineStr">
-        <is>
-          <t>Restore</t>
-        </is>
-      </c>
-      <c r="D524" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E524" s="7" t="inlineStr">
-        <is>
-          <t>备份里有当前版本不存在的表：{missing.joinToString()}。</t>
-        </is>
-      </c>
-      <c r="F524" s="5" t="n"/>
-    </row>
-    <row r="525">
-      <c r="A525" s="3" t="n">
-        <v>522</v>
-      </c>
-      <c r="B525" s="4" t="inlineStr">
-        <is>
-          <t>月付自动扣款</t>
-        </is>
-      </c>
-      <c r="C525" s="4" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="D525" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E525" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 期</t>
-        </is>
-      </c>
-      <c r="F525" s="5" t="n"/>
-    </row>
-    <row r="526">
-      <c r="A526" s="6" t="n">
-        <v>523</v>
-      </c>
-      <c r="B526" s="7" t="inlineStr">
-        <is>
-          <t>月付自动扣款</t>
-        </is>
-      </c>
-      <c r="C526" s="7" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="D526" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E526" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 第 </t>
-        </is>
-      </c>
-      <c r="F526" s="5" t="n"/>
-    </row>
-    <row r="527">
-      <c r="A527" s="6" t="n">
-        <v>524</v>
-      </c>
-      <c r="B527" s="7" t="inlineStr">
-        <is>
-          <t>月付自动扣款</t>
-        </is>
-      </c>
-      <c r="C527" s="7" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="D527" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E527" s="7" t="inlineStr">
-        <is>
-          <t>（含手续费）</t>
-        </is>
-      </c>
-      <c r="F527" s="5" t="n"/>
-    </row>
-    <row r="528">
-      <c r="A528" s="3" t="n">
-        <v>525</v>
-      </c>
-      <c r="B528" s="4" t="inlineStr">
-        <is>
-          <t>预算提醒</t>
-        </is>
-      </c>
-      <c r="C528" s="4" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D528" s="4" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E528" s="4" t="inlineStr">
-        <is>
-          <t>分类预算</t>
-        </is>
-      </c>
-      <c r="F528" s="5" t="n"/>
-    </row>
-    <row r="529">
-      <c r="A529" s="6" t="n">
-        <v>526</v>
-      </c>
-      <c r="B529" s="7" t="inlineStr">
-        <is>
-          <t>预算提醒</t>
-        </is>
-      </c>
-      <c r="C529" s="7" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D529" s="7" t="inlineStr">
-        <is>
-          <t>界面文字</t>
-        </is>
-      </c>
-      <c r="E529" s="7" t="inlineStr">
-        <is>
-          <t>总预算</t>
-        </is>
-      </c>
-      <c r="F529" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:F529"/>
+  <autoFilter ref="A3:F517"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -14991,7 +14678,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>共 526 条界面文字，23 条导出文件文字。</t>
+          <t>共 514 条界面文字，23 条导出文件文字。</t>
         </is>
       </c>
     </row>

--- a/tools/记账本文案.xlsx
+++ b/tools/记账本文案.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>app_name；导出与备份 · Prepare；导出与备份 · Prepare Backup 等5处</t>
+          <t>app_name；设置 · About Screen；桌面小组件 · Widget Body</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>记账本</t>
+          <t>随心记账</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>逐项说明记账本的各项功能</t>
+          <t>逐项说明随心记账的各项功能</t>
         </is>
       </c>
       <c r="F300" s="5" t="n"/>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="E353" s="7" t="inlineStr">
         <is>
-          <t>关于记账本</t>
+          <t>关于随心记账</t>
         </is>
       </c>
       <c r="F353" s="5" t="n"/>
@@ -11118,7 +11118,7 @@
       </c>
       <c r="E410" s="7" t="inlineStr">
         <is>
-          <t>记账本 · 本月</t>
+          <t>随心记账 · 本月</t>
         </is>
       </c>
       <c r="F410" s="5" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E412" s="7" t="inlineStr">
         <is>
-          <t>记账本 · 本月概览</t>
+          <t>随心记账 · 本月概览</t>
         </is>
       </c>
       <c r="F412" s="5" t="n"/>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>备份来自更新的记账本（格式 v{version}），当前版本读不了。</t>
+          <t>备份来自更新的随心记账（格式 v{version}），当前版本读不了。</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -14069,7 +14069,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>这个文件不是记账本备份。</t>
+          <t>这个文件不是随心记账备份。</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>这个文件不是记账本备份。</t>
+          <t>这个文件不是随心记账备份。</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
